--- a/results/01_pollution_assessment/MaxRel_Focus/tables/MaxRel_single_cutoff_metrics.xlsx
+++ b/results/01_pollution_assessment/MaxRel_Focus/tables/MaxRel_single_cutoff_metrics.xlsx
@@ -491,25 +491,25 @@
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>0.222662180183875</v>
+        <v>0.2061698637211829</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1362913113154167</v>
+        <v>0.1179665152457589</v>
       </c>
       <c r="F2" t="n">
-        <v>2.577977773072846</v>
+        <v>2.33743805971978</v>
       </c>
       <c r="G2" t="n">
-        <v>0.099</v>
+        <v>0.09</v>
       </c>
       <c r="H2" t="n">
-        <v>1.148871730851656</v>
+        <v>66.12282988418517</v>
       </c>
       <c r="I2" t="n">
-        <v>5.159707543970486</v>
+        <v>320.7201512904302</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1148871730851656</v>
+        <v>6.612282988418517</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
@@ -526,25 +526,25 @@
         <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1752240473125162</v>
+        <v>0.1311713264411049</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1163114792634102</v>
+        <v>0.06911213547261241</v>
       </c>
       <c r="F3" t="n">
-        <v>2.974306724610272</v>
+        <v>2.113648669827175</v>
       </c>
       <c r="G3" t="n">
-        <v>0.052</v>
+        <v>0.08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.38518634141258</v>
+        <v>63.0889414919785</v>
       </c>
       <c r="I3" t="n">
-        <v>7.905229691116926</v>
+        <v>480.965948913424</v>
       </c>
       <c r="J3" t="n">
-        <v>0.092345756094172</v>
+        <v>4.205929432798568</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
@@ -561,25 +561,25 @@
         <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1093494318773316</v>
+        <v>0.08174540935709358</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05986884475940557</v>
+        <v>0.03073126543248772</v>
       </c>
       <c r="F4" t="n">
-        <v>2.209946127290717</v>
+        <v>1.602406765423832</v>
       </c>
       <c r="G4" t="n">
-        <v>0.074</v>
+        <v>0.126</v>
       </c>
       <c r="H4" t="n">
-        <v>1.127034632886334</v>
+        <v>48.29786423305866</v>
       </c>
       <c r="I4" t="n">
-        <v>10.3067260024784</v>
+        <v>590.8327404915924</v>
       </c>
       <c r="J4" t="n">
-        <v>0.05931761225717546</v>
+        <v>2.541992854371509</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
@@ -596,25 +596,25 @@
         <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1530571682779909</v>
+        <v>0.1110425442237403</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1162335668987731</v>
+        <v>0.07239222005955503</v>
       </c>
       <c r="F5" t="n">
-        <v>4.156496446444049</v>
+        <v>2.873004214713322</v>
       </c>
       <c r="G5" t="n">
-        <v>0.008</v>
+        <v>0.015</v>
       </c>
       <c r="H5" t="n">
-        <v>1.910680738631067</v>
+        <v>77.45962196695983</v>
       </c>
       <c r="I5" t="n">
-        <v>12.48344497763595</v>
+        <v>697.5670677257358</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07961169744296115</v>
+        <v>3.227484248623324</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
@@ -631,25 +631,25 @@
         <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1463096779483338</v>
+        <v>0.09965726023995916</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1158207378750599</v>
+        <v>0.06750216239138618</v>
       </c>
       <c r="F6" t="n">
-        <v>4.798778757041375</v>
+        <v>3.099267827119431</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="H6" t="n">
-        <v>2.11594345607344</v>
+        <v>80.63011132010732</v>
       </c>
       <c r="I6" t="n">
-        <v>14.46208812530256</v>
+        <v>809.0741319394349</v>
       </c>
       <c r="J6" t="n">
-        <v>0.07296356745080824</v>
+        <v>2.780348666210597</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
@@ -666,25 +666,25 @@
         <v>34</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1082164139031273</v>
+        <v>0.07215398192094702</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08034817683759998</v>
+        <v>0.04315879385597665</v>
       </c>
       <c r="F7" t="n">
-        <v>3.883145304407861</v>
+        <v>2.488481252795097</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01</v>
+        <v>0.029</v>
       </c>
       <c r="H7" t="n">
-        <v>1.776285854899806</v>
+        <v>66.76816206482731</v>
       </c>
       <c r="I7" t="n">
-        <v>16.41419994280991</v>
+        <v>925.3565816780495</v>
       </c>
       <c r="J7" t="n">
-        <v>0.05382684408787291</v>
+        <v>2.023277638328101</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
@@ -701,25 +701,25 @@
         <v>39</v>
       </c>
       <c r="D8" t="n">
-        <v>0.08452065749891467</v>
+        <v>0.05691531067016023</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05977797256645301</v>
+        <v>0.03142653528286732</v>
       </c>
       <c r="F8" t="n">
-        <v>3.415985683430246</v>
+        <v>2.232955871961368</v>
       </c>
       <c r="G8" t="n">
-        <v>0.015</v>
+        <v>0.039</v>
       </c>
       <c r="H8" t="n">
-        <v>1.596590631089612</v>
+        <v>61.22917652251933</v>
       </c>
       <c r="I8" t="n">
-        <v>18.88994570481321</v>
+        <v>1075.794470794671</v>
       </c>
       <c r="J8" t="n">
-        <v>0.04201554292341084</v>
+        <v>1.611294119013667</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
@@ -736,25 +736,25 @@
         <v>44</v>
       </c>
       <c r="D9" t="n">
-        <v>0.05756454557691953</v>
+        <v>0.04239273948635495</v>
       </c>
       <c r="E9" t="n">
-        <v>0.035125606185894</v>
+        <v>0.0195925666169825</v>
       </c>
       <c r="F9" t="n">
-        <v>2.565386205372167</v>
+        <v>1.859316581906322</v>
       </c>
       <c r="G9" t="n">
-        <v>0.032</v>
+        <v>0.065</v>
       </c>
       <c r="H9" t="n">
-        <v>1.190680403195928</v>
+        <v>50.96902284751795</v>
       </c>
       <c r="I9" t="n">
-        <v>20.6842665266054</v>
+        <v>1202.305476481969</v>
       </c>
       <c r="J9" t="n">
-        <v>0.02769024193478901</v>
+        <v>1.185326112732976</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
@@ -771,25 +771,25 @@
         <v>48</v>
       </c>
       <c r="D10" t="n">
-        <v>0.05162593110166579</v>
+        <v>0.02757257959172427</v>
       </c>
       <c r="E10" t="n">
-        <v>0.03100910351691932</v>
+        <v>0.006432853061109522</v>
       </c>
       <c r="F10" t="n">
-        <v>2.504067654902535</v>
+        <v>1.304301621489449</v>
       </c>
       <c r="G10" t="n">
-        <v>0.044</v>
+        <v>0.231</v>
       </c>
       <c r="H10" t="n">
-        <v>1.17691040971595</v>
+        <v>36.24956604661268</v>
       </c>
       <c r="I10" t="n">
-        <v>22.7968849103813</v>
+        <v>1314.696215710363</v>
       </c>
       <c r="J10" t="n">
-        <v>0.02504064701523297</v>
+        <v>0.7712673626938866</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
@@ -806,25 +806,25 @@
         <v>53</v>
       </c>
       <c r="D11" t="n">
-        <v>0.03724210265435716</v>
+        <v>0.02954876796257323</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0183644968240505</v>
+        <v>0.01052031243242768</v>
       </c>
       <c r="F11" t="n">
-        <v>1.972819169397396</v>
+        <v>1.552872639387938</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1</v>
+        <v>0.144</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9174501013442912</v>
+        <v>41.97075885729143</v>
       </c>
       <c r="I11" t="n">
-        <v>24.63475571879274</v>
+        <v>1420.389469721784</v>
       </c>
       <c r="J11" t="n">
-        <v>0.01764327117969791</v>
+        <v>0.8071299780248347</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
@@ -841,25 +841,25 @@
         <v>58</v>
       </c>
       <c r="D12" t="n">
-        <v>0.01667011646626348</v>
+        <v>0.01435063263804923</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0008893457396961235</v>
+        <v>-0.003250248921985444</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9493523361214182</v>
+        <v>0.8153360153638137</v>
       </c>
       <c r="G12" t="n">
-        <v>0.401</v>
+        <v>0.529</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4630276981619289</v>
+        <v>22.75587353854971</v>
       </c>
       <c r="I12" t="n">
-        <v>27.77591260978839</v>
+        <v>1585.705251642694</v>
       </c>
       <c r="J12" t="n">
-        <v>0.00812329295020928</v>
+        <v>0.3992258515535038</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -876,25 +876,25 @@
         <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>0.01937073949452175</v>
+        <v>0.01701576438396714</v>
       </c>
       <c r="E13" t="n">
-        <v>0.003026918486097152</v>
+        <v>0.0006326937903666785</v>
       </c>
       <c r="F13" t="n">
-        <v>1.185202620888766</v>
+        <v>1.03861875505888</v>
       </c>
       <c r="G13" t="n">
-        <v>0.312</v>
+        <v>0.362</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5623608918330565</v>
+        <v>28.18580886114838</v>
       </c>
       <c r="I13" t="n">
-        <v>29.03146222125893</v>
+        <v>1656.452700279869</v>
       </c>
       <c r="J13" t="n">
-        <v>0.009219031013656662</v>
+        <v>0.4620624403466951</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -911,25 +911,25 @@
         <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>0.02953965331853715</v>
+        <v>0.02433946205984232</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0146094941388224</v>
+        <v>0.009329299937686053</v>
       </c>
       <c r="F14" t="n">
-        <v>1.978522329398325</v>
+        <v>1.621532256731272</v>
       </c>
       <c r="G14" t="n">
-        <v>0.092</v>
+        <v>0.117</v>
       </c>
       <c r="H14" t="n">
-        <v>0.887758279741376</v>
+        <v>42.37711597584027</v>
       </c>
       <c r="I14" t="n">
-        <v>30.05310421785747</v>
+        <v>1741.086794426664</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01345088302638449</v>
+        <v>0.6420775147854586</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -946,25 +946,25 @@
         <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>0.03348539125636515</v>
+        <v>0.02517660740418864</v>
       </c>
       <c r="E15" t="n">
-        <v>0.01967803970288473</v>
+        <v>0.01125055893853422</v>
       </c>
       <c r="F15" t="n">
-        <v>2.425185679285778</v>
+        <v>1.807878772379778</v>
       </c>
       <c r="G15" t="n">
-        <v>0.058</v>
+        <v>0.081</v>
       </c>
       <c r="H15" t="n">
-        <v>1.048689466936528</v>
+        <v>45.98476195033285</v>
       </c>
       <c r="I15" t="n">
-        <v>31.31782032671293</v>
+        <v>1826.487628459518</v>
       </c>
       <c r="J15" t="n">
-        <v>0.01477027418220462</v>
+        <v>0.647672703525815</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -981,25 +981,25 @@
         <v>76</v>
       </c>
       <c r="D16" t="n">
-        <v>0.02600351754822239</v>
+        <v>0.02021289450795234</v>
       </c>
       <c r="E16" t="n">
-        <v>0.01284140292049563</v>
+        <v>0.006972528217519258</v>
       </c>
       <c r="F16" t="n">
-        <v>1.975633724800157</v>
+        <v>1.52661142936486</v>
       </c>
       <c r="G16" t="n">
-        <v>0.105</v>
+        <v>0.157</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8703809012140351</v>
+        <v>39.08929550298586</v>
       </c>
       <c r="I16" t="n">
-        <v>33.47166011674965</v>
+        <v>1933.879162512177</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01160507868285381</v>
+        <v>0.521190606706478</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1016,25 +1016,25 @@
         <v>81</v>
       </c>
       <c r="D17" t="n">
-        <v>0.02896475761686937</v>
+        <v>0.02435790314121768</v>
       </c>
       <c r="E17" t="n">
-        <v>0.01667317227024734</v>
+        <v>0.01200800318097983</v>
       </c>
       <c r="F17" t="n">
-        <v>2.356470447063181</v>
+        <v>1.97231582601004</v>
       </c>
       <c r="G17" t="n">
-        <v>0.055</v>
+        <v>0.056</v>
       </c>
       <c r="H17" t="n">
-        <v>1.016121051267294</v>
+        <v>49.38935573607008</v>
       </c>
       <c r="I17" t="n">
-        <v>35.08128963853281</v>
+        <v>2027.652193611648</v>
       </c>
       <c r="J17" t="n">
-        <v>0.01270151314084117</v>
+        <v>0.6173669467008761</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
@@ -1051,25 +1051,25 @@
         <v>86</v>
       </c>
       <c r="D18" t="n">
-        <v>0.02349381045932126</v>
+        <v>0.02023141148609157</v>
       </c>
       <c r="E18" t="n">
-        <v>0.01186873677431322</v>
+        <v>0.008567499718068805</v>
       </c>
       <c r="F18" t="n">
-        <v>2.020960132890971</v>
+        <v>1.734530566456884</v>
       </c>
       <c r="G18" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.093</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8912071583713412</v>
+        <v>44.50842495777288</v>
       </c>
       <c r="I18" t="n">
-        <v>37.93370002343538</v>
+        <v>2199.966373496529</v>
       </c>
       <c r="J18" t="n">
-        <v>0.01048479009848636</v>
+        <v>0.5236285289149754</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
@@ -1086,25 +1086,25 @@
         <v>90</v>
       </c>
       <c r="D19" t="n">
-        <v>0.02642854827566471</v>
+        <v>0.02489670875664153</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0153652363242518</v>
+        <v>0.01381598953796692</v>
       </c>
       <c r="F19" t="n">
-        <v>2.388845979552218</v>
+        <v>2.246849528926126</v>
       </c>
       <c r="G19" t="n">
-        <v>0.064</v>
+        <v>0.04</v>
       </c>
       <c r="H19" t="n">
-        <v>1.026665090547786</v>
+        <v>55.99365516157191</v>
       </c>
       <c r="I19" t="n">
-        <v>38.84682124190434</v>
+        <v>2249.038445558988</v>
       </c>
       <c r="J19" t="n">
-        <v>0.01153556281514366</v>
+        <v>0.6291421928266511</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
@@ -1121,25 +1121,25 @@
         <v>95</v>
       </c>
       <c r="D20" t="n">
-        <v>0.005792108670301565</v>
+        <v>0.006162699678921424</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.004898298763351017</v>
+        <v>-0.00452372290517622</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5418042956967574</v>
+        <v>0.5766850066449825</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2488376649745365</v>
+        <v>15.47561277659862</v>
       </c>
       <c r="I20" t="n">
-        <v>42.96149798611786</v>
+        <v>2511.174255258714</v>
       </c>
       <c r="J20" t="n">
-        <v>0.002647209201856771</v>
+        <v>0.1646341784744534</v>
       </c>
       <c r="K20" t="n">
         <v>1</v>
@@ -1156,25 +1156,25 @@
         <v>100</v>
       </c>
       <c r="D21" t="n">
-        <v>0.008729339484913149</v>
+        <v>0.008956144542143706</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.001385667255036527</v>
+        <v>-0.001156547860487356</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8630087660185203</v>
+        <v>0.8856340315278882</v>
       </c>
       <c r="G21" t="n">
-        <v>0.454</v>
+        <v>0.451</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3930164102542864</v>
+        <v>23.73080638639154</v>
       </c>
       <c r="I21" t="n">
-        <v>45.02246830170068</v>
+        <v>2649.667641553207</v>
       </c>
       <c r="J21" t="n">
-        <v>0.003969862729841275</v>
+        <v>0.239705115014056</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
@@ -1191,25 +1191,25 @@
         <v>104</v>
       </c>
       <c r="D22" t="n">
-        <v>0.01110564417469292</v>
+        <v>0.01105249862390511</v>
       </c>
       <c r="E22" t="n">
-        <v>0.001410601470523298</v>
+        <v>0.001356934884923833</v>
       </c>
       <c r="F22" t="n">
-        <v>1.145497190014085</v>
+        <v>1.139954201885981</v>
       </c>
       <c r="G22" t="n">
-        <v>0.328</v>
+        <v>0.301</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5196343433410807</v>
+        <v>30.43616301258205</v>
       </c>
       <c r="I22" t="n">
-        <v>46.79011277213453</v>
+        <v>2753.781208056667</v>
       </c>
       <c r="J22" t="n">
-        <v>0.005044993624670687</v>
+        <v>0.2954967282774958</v>
       </c>
       <c r="K22" t="n">
         <v>1</v>
@@ -1226,25 +1226,25 @@
         <v>109</v>
       </c>
       <c r="D23" t="n">
-        <v>0.01437763158452431</v>
+        <v>0.01454725286666158</v>
       </c>
       <c r="E23" t="n">
-        <v>0.005166207580641458</v>
+        <v>0.005337414108406158</v>
       </c>
       <c r="F23" t="n">
-        <v>1.560847875253991</v>
+        <v>1.579533936315848</v>
       </c>
       <c r="G23" t="n">
-        <v>0.168</v>
+        <v>0.117</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7033619807569107</v>
+        <v>42.05368176200074</v>
       </c>
       <c r="I23" t="n">
-        <v>48.92057336578231</v>
+        <v>2890.833214178641</v>
       </c>
       <c r="J23" t="n">
-        <v>0.00651261093293436</v>
+        <v>0.3893859422407476</v>
       </c>
       <c r="K23" t="n">
         <v>1</v>
@@ -1261,25 +1261,25 @@
         <v>114</v>
       </c>
       <c r="D24" t="n">
-        <v>0.008922817498752615</v>
+        <v>0.0111382843521153</v>
       </c>
       <c r="E24" t="n">
-        <v>7.39140835629426e-05</v>
+        <v>0.002309161890973521</v>
       </c>
       <c r="F24" t="n">
-        <v>1.008352908840211</v>
+        <v>1.26153923010315</v>
       </c>
       <c r="G24" t="n">
-        <v>0.376</v>
+        <v>0.248</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4613504039273802</v>
+        <v>33.96646018664569</v>
       </c>
       <c r="I24" t="n">
-        <v>51.70456573743391</v>
+        <v>3049.523527399895</v>
       </c>
       <c r="J24" t="n">
-        <v>0.004082746937410444</v>
+        <v>0.3005881432446523</v>
       </c>
       <c r="K24" t="n">
         <v>1</v>
@@ -1296,25 +1296,25 @@
         <v>118</v>
       </c>
       <c r="D25" t="n">
-        <v>0.01033269317507599</v>
+        <v>0.01184888071673825</v>
       </c>
       <c r="E25" t="n">
-        <v>0.00180107846106814</v>
+        <v>0.003330336584986049</v>
       </c>
       <c r="F25" t="n">
-        <v>1.211106399133431</v>
+        <v>1.390951380127551</v>
       </c>
       <c r="G25" t="n">
-        <v>0.305</v>
+        <v>0.197</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5618065462880264</v>
+        <v>37.81241675340127</v>
       </c>
       <c r="I25" t="n">
-        <v>54.37174382020638</v>
+        <v>3191.22266966413</v>
       </c>
       <c r="J25" t="n">
-        <v>0.004801765352889113</v>
+        <v>0.3231830491743698</v>
       </c>
       <c r="K25" t="n">
         <v>1</v>
@@ -1331,25 +1331,25 @@
         <v>123</v>
       </c>
       <c r="D26" t="n">
-        <v>0.009799848169250875</v>
+        <v>0.01058607599404815</v>
       </c>
       <c r="E26" t="n">
-        <v>0.001616375840071127</v>
+        <v>0.002409101415486559</v>
       </c>
       <c r="F26" t="n">
-        <v>1.197517114380363</v>
+        <v>1.294620142491669</v>
       </c>
       <c r="G26" t="n">
-        <v>0.276</v>
+        <v>0.224</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5492971917468452</v>
+        <v>34.88784623067633</v>
       </c>
       <c r="I26" t="n">
-        <v>56.05160225546993</v>
+        <v>3295.635346873709</v>
       </c>
       <c r="J26" t="n">
-        <v>0.00450243599792496</v>
+        <v>0.2859659527104616</v>
       </c>
       <c r="K26" t="n">
         <v>1</v>
@@ -1366,25 +1366,25 @@
         <v>128</v>
       </c>
       <c r="D27" t="n">
-        <v>0.009006783345452593</v>
+        <v>0.01117586790994968</v>
       </c>
       <c r="E27" t="n">
-        <v>0.001141757816448208</v>
+        <v>0.0033280573378065</v>
       </c>
       <c r="F27" t="n">
-        <v>1.145168990518558</v>
+        <v>1.424074626574164</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3</v>
+        <v>0.177</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5361707256499857</v>
+        <v>38.9520186328758</v>
       </c>
       <c r="I27" t="n">
-        <v>59.52965726889514</v>
+        <v>3485.368559000011</v>
       </c>
       <c r="J27" t="n">
-        <v>0.004221816737401461</v>
+        <v>0.3067088081328804</v>
       </c>
       <c r="K27" t="n">
         <v>1</v>
@@ -1401,25 +1401,25 @@
         <v>132</v>
       </c>
       <c r="D28" t="n">
-        <v>0.00894214078658428</v>
+        <v>0.01279508108919393</v>
       </c>
       <c r="E28" t="n">
-        <v>0.001318618792634951</v>
+        <v>0.005201197097572385</v>
       </c>
       <c r="F28" t="n">
-        <v>1.172967139555902</v>
+        <v>1.684919219639237</v>
       </c>
       <c r="G28" t="n">
-        <v>0.296</v>
+        <v>0.112</v>
       </c>
       <c r="H28" t="n">
-        <v>0.5460508445706111</v>
+        <v>45.39209230439621</v>
       </c>
       <c r="I28" t="n">
-        <v>61.06489012003038</v>
+        <v>3547.620526041999</v>
       </c>
       <c r="J28" t="n">
-        <v>0.004168327057790927</v>
+        <v>0.3465045214076047</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
@@ -1436,25 +1436,25 @@
         <v>137</v>
       </c>
       <c r="D29" t="n">
-        <v>0.008342347698022855</v>
+        <v>0.01201886192957595</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0009967354587491206</v>
+        <v>0.004700483129054356</v>
       </c>
       <c r="F29" t="n">
-        <v>1.135691270690797</v>
+        <v>1.64228475420256</v>
       </c>
       <c r="G29" t="n">
-        <v>0.32</v>
+        <v>0.118</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5311599822459074</v>
+        <v>44.20397310442299</v>
       </c>
       <c r="I29" t="n">
-        <v>63.67032416687606</v>
+        <v>3677.883427185905</v>
       </c>
       <c r="J29" t="n">
-        <v>0.003905588104749319</v>
+        <v>0.3250292140031103</v>
       </c>
       <c r="K29" t="n">
         <v>1</v>
@@ -1471,25 +1471,25 @@
         <v>142</v>
       </c>
       <c r="D30" t="n">
-        <v>0.003901083396455929</v>
+        <v>0.008089688255415419</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.003213908864998061</v>
+        <v>0.001004614600097042</v>
       </c>
       <c r="F30" t="n">
-        <v>0.5482906028711234</v>
+        <v>1.14179310603819</v>
       </c>
       <c r="G30" t="n">
-        <v>0.705</v>
+        <v>0.291</v>
       </c>
       <c r="H30" t="n">
-        <v>0.2593530682680876</v>
+        <v>30.78927007345581</v>
       </c>
       <c r="I30" t="n">
-        <v>66.48231834871964</v>
+        <v>3805.989687284276</v>
       </c>
       <c r="J30" t="n">
-        <v>0.001839383462894238</v>
+        <v>0.2183636175422398</v>
       </c>
       <c r="K30" t="n">
         <v>1</v>
@@ -1506,25 +1506,25 @@
         <v>146</v>
       </c>
       <c r="D31" t="n">
-        <v>0.005619070028679425</v>
+        <v>0.009698270505655943</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.001286353096121351</v>
+        <v>0.002821175161945244</v>
       </c>
       <c r="F31" t="n">
-        <v>0.81371842494322</v>
+        <v>1.410227722744204</v>
       </c>
       <c r="G31" t="n">
-        <v>0.478</v>
+        <v>0.157</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3868253605874158</v>
+        <v>37.63966531187638</v>
       </c>
       <c r="I31" t="n">
-        <v>68.84152690980542</v>
+        <v>3881.069855694917</v>
       </c>
       <c r="J31" t="n">
-        <v>0.002667761107499419</v>
+        <v>0.2595838987025956</v>
       </c>
       <c r="K31" t="n">
         <v>1</v>
@@ -1541,25 +1541,25 @@
         <v>151</v>
       </c>
       <c r="D32" t="n">
-        <v>0.007397589737627497</v>
+        <v>0.009930706036701412</v>
       </c>
       <c r="E32" t="n">
-        <v>0.000735828594926935</v>
+        <v>0.003285945674531554</v>
       </c>
       <c r="F32" t="n">
-        <v>1.110455565602691</v>
+        <v>1.49451680654118</v>
       </c>
       <c r="G32" t="n">
-        <v>0.343</v>
+        <v>0.181</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5257634751017233</v>
+        <v>39.85340503200516</v>
       </c>
       <c r="I32" t="n">
-        <v>71.07226728557976</v>
+        <v>4013.149204569837</v>
       </c>
       <c r="J32" t="n">
-        <v>0.00350508983401149</v>
+        <v>0.2656893668800343</v>
       </c>
       <c r="K32" t="n">
         <v>1</v>
@@ -1576,25 +1576,25 @@
         <v>156</v>
       </c>
       <c r="D33" t="n">
-        <v>0.008832818445900956</v>
+        <v>0.01173671026521023</v>
       </c>
       <c r="E33" t="n">
-        <v>0.002396667916328865</v>
+        <v>0.005319416176023273</v>
       </c>
       <c r="F33" t="n">
-        <v>1.372375988615704</v>
+        <v>1.828918871738547</v>
       </c>
       <c r="G33" t="n">
-        <v>0.231</v>
+        <v>0.098</v>
       </c>
       <c r="H33" t="n">
-        <v>0.6548419674462668</v>
+        <v>49.04564610370941</v>
       </c>
       <c r="I33" t="n">
-        <v>74.13737432248017</v>
+        <v>4178.823963056301</v>
       </c>
       <c r="J33" t="n">
-        <v>0.004224786886750109</v>
+        <v>0.3164235232497381</v>
       </c>
       <c r="K33" t="n">
         <v>1</v>
@@ -1611,25 +1611,25 @@
         <v>160</v>
       </c>
       <c r="D34" t="n">
-        <v>0.009674532513944652</v>
+        <v>0.01252016915775237</v>
       </c>
       <c r="E34" t="n">
-        <v>0.003406649808336715</v>
+        <v>0.006270296810649501</v>
       </c>
       <c r="F34" t="n">
-        <v>1.543508863892545</v>
+        <v>2.00326798091423</v>
       </c>
       <c r="G34" t="n">
-        <v>0.191</v>
+        <v>0.075</v>
       </c>
       <c r="H34" t="n">
-        <v>0.7325280961351053</v>
+        <v>53.46925951789868</v>
       </c>
       <c r="I34" t="n">
-        <v>75.71715688373116</v>
+        <v>4270.649928462908</v>
       </c>
       <c r="J34" t="n">
-        <v>0.004607094944245944</v>
+        <v>0.3362846510559667</v>
       </c>
       <c r="K34" t="n">
         <v>1</v>
@@ -1646,25 +1646,25 @@
         <v>165</v>
       </c>
       <c r="D35" t="n">
-        <v>0.01059543121904793</v>
+        <v>0.01263425400821769</v>
       </c>
       <c r="E35" t="n">
-        <v>0.004525464539410273</v>
+        <v>0.006576795443851036</v>
       </c>
       <c r="F35" t="n">
-        <v>1.745550145207761</v>
+        <v>2.085735110519647</v>
       </c>
       <c r="G35" t="n">
-        <v>0.123</v>
+        <v>0.053</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8295051195886776</v>
+        <v>56.19034425041148</v>
       </c>
       <c r="I35" t="n">
-        <v>78.28894383245442</v>
+        <v>4447.460389340251</v>
       </c>
       <c r="J35" t="n">
-        <v>0.005057958046272423</v>
+        <v>0.3426240503073871</v>
       </c>
       <c r="K35" t="n">
         <v>1</v>
@@ -1681,25 +1681,25 @@
         <v>170</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0130365987489762</v>
+        <v>0.01269954577927633</v>
       </c>
       <c r="E36" t="n">
-        <v>0.007161816598672543</v>
+        <v>0.006822757361295895</v>
       </c>
       <c r="F36" t="n">
-        <v>2.219077816919941</v>
+        <v>2.160966990137175</v>
       </c>
       <c r="G36" t="n">
-        <v>0.078</v>
+        <v>0.055</v>
       </c>
       <c r="H36" t="n">
-        <v>1.053143079681808</v>
+        <v>58.09669128316457</v>
       </c>
       <c r="I36" t="n">
-        <v>80.78357706334363</v>
+        <v>4574.706236971821</v>
       </c>
       <c r="J36" t="n">
-        <v>0.006231615856105376</v>
+        <v>0.343767404042394</v>
       </c>
       <c r="K36" t="n">
         <v>1</v>
@@ -1716,25 +1716,25 @@
         <v>174</v>
       </c>
       <c r="D37" t="n">
-        <v>0.01170849513768986</v>
+        <v>0.01041264552989096</v>
       </c>
       <c r="E37" t="n">
-        <v>0.005962614295467183</v>
+        <v>0.004659230678320525</v>
       </c>
       <c r="F37" t="n">
-        <v>2.037719796006169</v>
+        <v>1.809820045750536</v>
       </c>
       <c r="G37" t="n">
-        <v>0.08</v>
+        <v>0.082</v>
       </c>
       <c r="H37" t="n">
-        <v>0.9742787516666839</v>
+        <v>49.20718485225651</v>
       </c>
       <c r="I37" t="n">
-        <v>83.21127012560841</v>
+        <v>4725.714009086392</v>
       </c>
       <c r="J37" t="n">
-        <v>0.005631669084778517</v>
+        <v>0.2844345945217138</v>
       </c>
       <c r="K37" t="n">
         <v>1</v>
@@ -1751,25 +1751,25 @@
         <v>179</v>
       </c>
       <c r="D38" t="n">
-        <v>0.009872934009548483</v>
+        <v>0.00952153771352689</v>
       </c>
       <c r="E38" t="n">
-        <v>0.004278995783613682</v>
+        <v>0.003925614197784033</v>
       </c>
       <c r="F38" t="n">
-        <v>1.764934400557973</v>
+        <v>1.701513197373111</v>
       </c>
       <c r="G38" t="n">
-        <v>0.138</v>
+        <v>0.117</v>
       </c>
       <c r="H38" t="n">
-        <v>0.8514286165613616</v>
+        <v>46.45932948487022</v>
       </c>
       <c r="I38" t="n">
-        <v>86.23866175322485</v>
+        <v>4879.393526832037</v>
       </c>
       <c r="J38" t="n">
-        <v>0.004783306834614393</v>
+        <v>0.2610074690161249</v>
       </c>
       <c r="K38" t="n">
         <v>1</v>
@@ -1786,25 +1786,25 @@
         <v>184</v>
       </c>
       <c r="D39" t="n">
-        <v>0.008349824949060291</v>
+        <v>0.01061112874226849</v>
       </c>
       <c r="E39" t="n">
-        <v>0.002901197613615625</v>
+        <v>0.00517492615294024</v>
       </c>
       <c r="F39" t="n">
-        <v>1.532463946422346</v>
+        <v>1.951937693252858</v>
       </c>
       <c r="G39" t="n">
-        <v>0.185</v>
+        <v>0.063</v>
       </c>
       <c r="H39" t="n">
-        <v>0.7372132562340495</v>
+        <v>53.04389700468506</v>
       </c>
       <c r="I39" t="n">
-        <v>88.29086366858712</v>
+        <v>4998.892982363828</v>
       </c>
       <c r="J39" t="n">
-        <v>0.004028487738983879</v>
+        <v>0.289857360681339</v>
       </c>
       <c r="K39" t="n">
         <v>1</v>
@@ -1821,25 +1821,25 @@
         <v>188</v>
       </c>
       <c r="D40" t="n">
-        <v>0.007770174567283451</v>
+        <v>0.00960261598576463</v>
       </c>
       <c r="E40" t="n">
-        <v>0.002435605613344105</v>
+        <v>0.004277898867408481</v>
       </c>
       <c r="F40" t="n">
-        <v>1.456570274819587</v>
+        <v>1.803403969135029</v>
       </c>
       <c r="G40" t="n">
-        <v>0.188</v>
+        <v>0.099</v>
       </c>
       <c r="H40" t="n">
-        <v>0.7083616486909513</v>
+        <v>49.67623754817089</v>
       </c>
       <c r="I40" t="n">
-        <v>91.16418718229689</v>
+        <v>5173.198389044535</v>
       </c>
       <c r="J40" t="n">
-        <v>0.003788030206903484</v>
+        <v>0.2656483291346036</v>
       </c>
       <c r="K40" t="n">
         <v>1</v>
@@ -1856,25 +1856,25 @@
         <v>193</v>
       </c>
       <c r="D41" t="n">
-        <v>0.005834765582070787</v>
+        <v>0.009220463866310058</v>
       </c>
       <c r="E41" t="n">
-        <v>0.000629711998730853</v>
+        <v>0.004033136451997543</v>
       </c>
       <c r="F41" t="n">
-        <v>1.120980886872403</v>
+        <v>1.777497954123659</v>
       </c>
       <c r="G41" t="n">
-        <v>0.318</v>
+        <v>0.128</v>
       </c>
       <c r="H41" t="n">
-        <v>0.541096653286825</v>
+        <v>48.68313148299291</v>
       </c>
       <c r="I41" t="n">
-        <v>92.73665679895012</v>
+        <v>5279.900468009256</v>
       </c>
       <c r="J41" t="n">
-        <v>0.00281821173586888</v>
+        <v>0.2535579764739214</v>
       </c>
       <c r="K41" t="n">
         <v>1</v>
@@ -1891,25 +1891,25 @@
         <v>198</v>
       </c>
       <c r="D42" t="n">
-        <v>0.007279597071666978</v>
+        <v>0.009279146731975878</v>
       </c>
       <c r="E42" t="n">
-        <v>0.002214697056726611</v>
+        <v>0.004224448501016553</v>
       </c>
       <c r="F42" t="n">
-        <v>1.437263726864021</v>
+        <v>1.835746924542879</v>
       </c>
       <c r="G42" t="n">
-        <v>0.191</v>
+        <v>0.09</v>
       </c>
       <c r="H42" t="n">
-        <v>0.6838071222974269</v>
+        <v>49.56495394095769</v>
       </c>
       <c r="I42" t="n">
-        <v>93.93474880071071</v>
+        <v>5341.542209927255</v>
       </c>
       <c r="J42" t="n">
-        <v>0.00347110214364176</v>
+        <v>0.2515987509693285</v>
       </c>
       <c r="K42" t="n">
         <v>1</v>
@@ -1926,25 +1926,25 @@
         <v>202</v>
       </c>
       <c r="D43" t="n">
-        <v>0.008596200814078428</v>
+        <v>0.009376949373318497</v>
       </c>
       <c r="E43" t="n">
-        <v>0.003639181818148929</v>
+        <v>0.004423834120185099</v>
       </c>
       <c r="F43" t="n">
-        <v>1.734147240738252</v>
+        <v>1.893141769189908</v>
       </c>
       <c r="G43" t="n">
-        <v>0.139</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="H43" t="n">
-        <v>0.8195042240557497</v>
+        <v>50.84361888870838</v>
       </c>
       <c r="I43" t="n">
-        <v>95.33330383738904</v>
+        <v>5422.191894666788</v>
       </c>
       <c r="J43" t="n">
-        <v>0.004077135443063431</v>
+        <v>0.2529533278045193</v>
       </c>
       <c r="K43" t="n">
         <v>1</v>
@@ -1961,25 +1961,25 @@
         <v>207</v>
       </c>
       <c r="D44" t="n">
-        <v>0.01175550813124048</v>
+        <v>0.009945037353682556</v>
       </c>
       <c r="E44" t="n">
-        <v>0.00693480329285634</v>
+        <v>0.005115500950529817</v>
       </c>
       <c r="F44" t="n">
-        <v>2.438545508457369</v>
+        <v>2.059211593723642</v>
       </c>
       <c r="G44" t="n">
-        <v>0.056</v>
+        <v>0.062</v>
       </c>
       <c r="H44" t="n">
-        <v>1.140902339753317</v>
+        <v>54.98775644691005</v>
       </c>
       <c r="I44" t="n">
-        <v>97.05257544089891</v>
+        <v>5529.165400927186</v>
       </c>
       <c r="J44" t="n">
-        <v>0.00553836087258892</v>
+        <v>0.2669308565383981</v>
       </c>
       <c r="K44" t="n">
         <v>1</v>
@@ -1996,25 +1996,25 @@
         <v>212</v>
       </c>
       <c r="D45" t="n">
-        <v>0.01119843204426694</v>
+        <v>0.01012880468910244</v>
       </c>
       <c r="E45" t="n">
-        <v>0.006489853149239666</v>
+        <v>0.005415132330479189</v>
       </c>
       <c r="F45" t="n">
-        <v>2.378304005077525</v>
+        <v>2.148813901028255</v>
       </c>
       <c r="G45" t="n">
-        <v>0.055</v>
+        <v>0.035</v>
       </c>
       <c r="H45" t="n">
-        <v>1.104724568366018</v>
+        <v>57.38866366677688</v>
       </c>
       <c r="I45" t="n">
-        <v>98.6499327762215</v>
+        <v>5665.887084240181</v>
       </c>
       <c r="J45" t="n">
-        <v>0.005235661461450321</v>
+        <v>0.2719841879942033</v>
       </c>
       <c r="K45" t="n">
         <v>1</v>
@@ -2031,25 +2031,25 @@
         <v>216</v>
       </c>
       <c r="D46" t="n">
-        <v>0.01108652096448152</v>
+        <v>0.01067950386429954</v>
       </c>
       <c r="E46" t="n">
-        <v>0.006465429940951006</v>
+        <v>0.006056510891702671</v>
       </c>
       <c r="F46" t="n">
-        <v>2.399113306366241</v>
+        <v>2.31008438204501</v>
       </c>
       <c r="G46" t="n">
-        <v>0.06</v>
+        <v>0.041</v>
       </c>
       <c r="H46" t="n">
-        <v>1.108705545796112</v>
+        <v>61.55508511026783</v>
       </c>
       <c r="I46" t="n">
-        <v>100.0048211109807</v>
+        <v>5763.852505923987</v>
       </c>
       <c r="J46" t="n">
-        <v>0.00515676998044703</v>
+        <v>0.2863027214431061</v>
       </c>
       <c r="K46" t="n">
         <v>1</v>
@@ -2066,25 +2066,25 @@
         <v>221</v>
       </c>
       <c r="D47" t="n">
-        <v>0.01461025642785179</v>
+        <v>0.01125881751922611</v>
       </c>
       <c r="E47" t="n">
-        <v>0.01011075988186028</v>
+        <v>0.006744017599222607</v>
       </c>
       <c r="F47" t="n">
-        <v>3.247086930396155</v>
+        <v>2.493757800726039</v>
       </c>
       <c r="G47" t="n">
-        <v>0.02</v>
+        <v>0.034</v>
       </c>
       <c r="H47" t="n">
-        <v>1.494533964315409</v>
+        <v>66.2635817407685</v>
       </c>
       <c r="I47" t="n">
-        <v>102.2934793578539</v>
+        <v>5885.483233706697</v>
       </c>
       <c r="J47" t="n">
-        <v>0.006793336201433679</v>
+        <v>0.3011980988216752</v>
       </c>
       <c r="K47" t="n">
         <v>1</v>
@@ -2101,25 +2101,25 @@
         <v>226</v>
       </c>
       <c r="D48" t="n">
-        <v>0.01739285843232522</v>
+        <v>0.01227300816846976</v>
       </c>
       <c r="E48" t="n">
-        <v>0.01300621940746938</v>
+        <v>0.007863512669221806</v>
       </c>
       <c r="F48" t="n">
-        <v>3.964962317111882</v>
+        <v>2.783313458549415</v>
       </c>
       <c r="G48" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.014</v>
       </c>
       <c r="H48" t="n">
-        <v>1.80257012606895</v>
+        <v>73.5738410639634</v>
       </c>
       <c r="I48" t="n">
-        <v>103.6385211253609</v>
+        <v>5994.768361108068</v>
       </c>
       <c r="J48" t="n">
-        <v>0.008011422782528669</v>
+        <v>0.3269948491731707</v>
       </c>
       <c r="K48" t="n">
         <v>1</v>
@@ -2136,25 +2136,25 @@
         <v>230</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0224822611999833</v>
+        <v>0.01379958402038184</v>
       </c>
       <c r="E49" t="n">
-        <v>0.01819490269647461</v>
+        <v>0.009474143599418672</v>
       </c>
       <c r="F49" t="n">
-        <v>5.243849139647047</v>
+        <v>3.190330388901482</v>
       </c>
       <c r="G49" t="n">
-        <v>0.001</v>
+        <v>0.007</v>
       </c>
       <c r="H49" t="n">
-        <v>2.355594557233183</v>
+        <v>83.58908971965155</v>
       </c>
       <c r="I49" t="n">
-        <v>104.7756956597823</v>
+        <v>6057.363004289939</v>
       </c>
       <c r="J49" t="n">
-        <v>0.01028643911455538</v>
+        <v>0.3650178590377797</v>
       </c>
       <c r="K49" t="n">
         <v>1</v>

--- a/results/01_pollution_assessment/MaxRel_Focus/tables/MaxRel_single_cutoff_metrics.xlsx
+++ b/results/01_pollution_assessment/MaxRel_Focus/tables/MaxRel_single_cutoff_metrics.xlsx
@@ -488,28 +488,28 @@
         <v>0.05</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2061698637211829</v>
+        <v>0.07763835896446926</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1179665152457589</v>
+        <v>0.006687463500197666</v>
       </c>
       <c r="F2" t="n">
-        <v>2.33743805971978</v>
+        <v>1.094254814635359</v>
       </c>
       <c r="G2" t="n">
-        <v>0.09</v>
+        <v>0.364</v>
       </c>
       <c r="H2" t="n">
-        <v>66.12282988418517</v>
+        <v>24.28332371666796</v>
       </c>
       <c r="I2" t="n">
-        <v>320.7201512904302</v>
+        <v>312.7748195680061</v>
       </c>
       <c r="J2" t="n">
-        <v>6.612282988418517</v>
+        <v>1.73452312261914</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
@@ -523,28 +523,28 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1311713264411049</v>
+        <v>0.01722907575536903</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06911213547261241</v>
+        <v>-0.03449570973119043</v>
       </c>
       <c r="F3" t="n">
-        <v>2.113648669827175</v>
+        <v>0.3330912944983782</v>
       </c>
       <c r="G3" t="n">
-        <v>0.08</v>
+        <v>0.928</v>
       </c>
       <c r="H3" t="n">
-        <v>63.0889414919785</v>
+        <v>7.734815706493755</v>
       </c>
       <c r="I3" t="n">
-        <v>480.965948913424</v>
+        <v>448.9396771085287</v>
       </c>
       <c r="J3" t="n">
-        <v>4.205929432798568</v>
+        <v>0.3867407853246878</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
@@ -558,28 +558,28 @@
         <v>0.09</v>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D4" t="n">
-        <v>0.08174540935709358</v>
+        <v>0.05449831769570292</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03073126543248772</v>
+        <v>0.01667825040353099</v>
       </c>
       <c r="F4" t="n">
-        <v>1.602406765423832</v>
+        <v>1.440989442844888</v>
       </c>
       <c r="G4" t="n">
-        <v>0.126</v>
+        <v>0.192</v>
       </c>
       <c r="H4" t="n">
-        <v>48.29786423305866</v>
+        <v>29.71469348874748</v>
       </c>
       <c r="I4" t="n">
-        <v>590.8327404915924</v>
+        <v>545.2405642071851</v>
       </c>
       <c r="J4" t="n">
-        <v>2.541992854371509</v>
+        <v>1.142872826490288</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
@@ -593,28 +593,28 @@
         <v>0.11</v>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1110425442237403</v>
+        <v>0.02525454316955128</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07239222005955503</v>
+        <v>-0.005206252356400265</v>
       </c>
       <c r="F5" t="n">
-        <v>2.873004214713322</v>
+        <v>0.8290835066351208</v>
       </c>
       <c r="G5" t="n">
-        <v>0.015</v>
+        <v>0.519</v>
       </c>
       <c r="H5" t="n">
-        <v>77.45962196695983</v>
+        <v>19.47134374649659</v>
       </c>
       <c r="I5" t="n">
-        <v>697.5670677257358</v>
+        <v>771.0036018379717</v>
       </c>
       <c r="J5" t="n">
-        <v>3.227484248623324</v>
+        <v>0.5900407195908056</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
@@ -628,28 +628,28 @@
         <v>0.13</v>
       </c>
       <c r="C6" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D6" t="n">
-        <v>0.09965726023995916</v>
+        <v>0.008368066182942632</v>
       </c>
       <c r="E6" t="n">
-        <v>0.06750216239138618</v>
+        <v>-0.01772751102276948</v>
       </c>
       <c r="F6" t="n">
-        <v>3.099267827119431</v>
+        <v>0.3206699019139134</v>
       </c>
       <c r="G6" t="n">
-        <v>0.005</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>80.63011132010732</v>
+        <v>7.810032493380561</v>
       </c>
       <c r="I6" t="n">
-        <v>809.0741319394349</v>
+        <v>933.3139010420878</v>
       </c>
       <c r="J6" t="n">
-        <v>2.780348666210597</v>
+        <v>0.2002572434200144</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
@@ -663,28 +663,28 @@
         <v>0.15</v>
       </c>
       <c r="C7" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D7" t="n">
-        <v>0.07215398192094702</v>
+        <v>0.02802271415093008</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04315879385597665</v>
+        <v>0.005932321290723963</v>
       </c>
       <c r="F7" t="n">
-        <v>2.488481252795097</v>
+        <v>1.268547568541005</v>
       </c>
       <c r="G7" t="n">
-        <v>0.029</v>
+        <v>0.275</v>
       </c>
       <c r="H7" t="n">
-        <v>66.76816206482731</v>
+        <v>34.60614743729575</v>
       </c>
       <c r="I7" t="n">
-        <v>925.3565816780495</v>
+        <v>1234.932035880156</v>
       </c>
       <c r="J7" t="n">
-        <v>2.023277638328101</v>
+        <v>0.7690254986065722</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
@@ -698,28 +698,28 @@
         <v>0.17</v>
       </c>
       <c r="C8" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05691531067016023</v>
+        <v>0.01453432716183859</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03142653528286732</v>
+        <v>-0.005174986294924633</v>
       </c>
       <c r="F8" t="n">
-        <v>2.232955871961368</v>
+        <v>0.737434471967929</v>
       </c>
       <c r="G8" t="n">
-        <v>0.039</v>
+        <v>0.569</v>
       </c>
       <c r="H8" t="n">
-        <v>61.22917652251933</v>
+        <v>19.86282721503144</v>
       </c>
       <c r="I8" t="n">
-        <v>1075.794470794671</v>
+        <v>1366.614841805914</v>
       </c>
       <c r="J8" t="n">
-        <v>1.611294119013667</v>
+        <v>0.389467200294734</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
@@ -733,28 +733,28 @@
         <v>0.19</v>
       </c>
       <c r="C9" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D9" t="n">
-        <v>0.04239273948635495</v>
+        <v>0.0167034468117795</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0195925666169825</v>
+        <v>-0.0008554202094386287</v>
       </c>
       <c r="F9" t="n">
-        <v>1.859316581906322</v>
+        <v>0.9512827218063085</v>
       </c>
       <c r="G9" t="n">
-        <v>0.065</v>
+        <v>0.413</v>
       </c>
       <c r="H9" t="n">
-        <v>50.96902284751795</v>
+        <v>26.04705252401973</v>
       </c>
       <c r="I9" t="n">
-        <v>1202.305476481969</v>
+        <v>1559.381893900544</v>
       </c>
       <c r="J9" t="n">
-        <v>1.185326112732976</v>
+        <v>0.4569658337547322</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
@@ -768,28 +768,28 @@
         <v>0.21</v>
       </c>
       <c r="C10" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="D10" t="n">
-        <v>0.02757257959172427</v>
+        <v>0.009001018187044039</v>
       </c>
       <c r="E10" t="n">
-        <v>0.006432853061109522</v>
+        <v>-0.006729124381415597</v>
       </c>
       <c r="F10" t="n">
-        <v>1.304301621489449</v>
+        <v>0.5722146603484644</v>
       </c>
       <c r="G10" t="n">
-        <v>0.231</v>
+        <v>0.711</v>
       </c>
       <c r="H10" t="n">
-        <v>36.24956604661268</v>
+        <v>15.85535975380239</v>
       </c>
       <c r="I10" t="n">
-        <v>1314.696215710363</v>
+        <v>1761.507356648207</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7712673626938866</v>
+        <v>0.2477399961531621</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
@@ -803,28 +803,28 @@
         <v>0.23</v>
       </c>
       <c r="C11" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="D11" t="n">
-        <v>0.02954876796257323</v>
+        <v>0.007459376398952546</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01052031243242768</v>
+        <v>-0.006925270319903198</v>
       </c>
       <c r="F11" t="n">
-        <v>1.552872639387938</v>
+        <v>0.518565144125132</v>
       </c>
       <c r="G11" t="n">
-        <v>0.144</v>
+        <v>0.777</v>
       </c>
       <c r="H11" t="n">
-        <v>41.97075885729143</v>
+        <v>14.02531355104338</v>
       </c>
       <c r="I11" t="n">
-        <v>1420.389469721784</v>
+        <v>1880.226013666884</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8071299780248347</v>
+        <v>0.2003616221577626</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
@@ -838,28 +838,28 @@
         <v>0.25</v>
       </c>
       <c r="C12" t="n">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>0.01435063263804923</v>
+        <v>0.01313965245593372</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.003250248921985444</v>
+        <v>-1.848551132055398e-05</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8153360153638137</v>
+        <v>0.9985951271094357</v>
       </c>
       <c r="G12" t="n">
-        <v>0.529</v>
+        <v>0.387</v>
       </c>
       <c r="H12" t="n">
-        <v>22.75587353854971</v>
+        <v>26.56245483384818</v>
       </c>
       <c r="I12" t="n">
-        <v>1585.705251642694</v>
+        <v>2021.549270266496</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3992258515535038</v>
+        <v>0.349505984655897</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -873,28 +873,28 @@
         <v>0.27</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="D13" t="n">
-        <v>0.01701576438396714</v>
+        <v>0.01392162367423972</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0006326937903666785</v>
+        <v>0.00174781655910683</v>
       </c>
       <c r="F13" t="n">
-        <v>1.03861875505888</v>
+        <v>1.143571895182587</v>
       </c>
       <c r="G13" t="n">
-        <v>0.362</v>
+        <v>0.309</v>
       </c>
       <c r="H13" t="n">
-        <v>28.18580886114838</v>
+        <v>31.30188298041526</v>
       </c>
       <c r="I13" t="n">
-        <v>1656.452700279869</v>
+        <v>2248.436225031395</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4620624403466951</v>
+        <v>0.3817302802489665</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -908,28 +908,28 @@
         <v>0.29</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>0.02433946205984232</v>
+        <v>0.01320682150051547</v>
       </c>
       <c r="E14" t="n">
-        <v>0.009329299937686053</v>
+        <v>0.001864371172935031</v>
       </c>
       <c r="F14" t="n">
-        <v>1.621532256731272</v>
+        <v>1.164371111981137</v>
       </c>
       <c r="G14" t="n">
-        <v>0.117</v>
+        <v>0.283</v>
       </c>
       <c r="H14" t="n">
-        <v>42.37711597584027</v>
+        <v>31.88663957785198</v>
       </c>
       <c r="I14" t="n">
-        <v>1741.086794426664</v>
+        <v>2414.406795503932</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6420775147854586</v>
+        <v>0.362348177021045</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -943,28 +943,28 @@
         <v>0.31</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="D15" t="n">
-        <v>0.02517660740418864</v>
+        <v>0.01252097777318102</v>
       </c>
       <c r="E15" t="n">
-        <v>0.01125055893853422</v>
+        <v>0.002015881792044594</v>
       </c>
       <c r="F15" t="n">
-        <v>1.807878772379778</v>
+        <v>1.191895609108617</v>
       </c>
       <c r="G15" t="n">
-        <v>0.081</v>
+        <v>0.273</v>
       </c>
       <c r="H15" t="n">
-        <v>45.98476195033285</v>
+        <v>32.34145634112159</v>
       </c>
       <c r="I15" t="n">
-        <v>1826.487628459518</v>
+        <v>2582.981690966221</v>
       </c>
       <c r="J15" t="n">
-        <v>0.647672703525815</v>
+        <v>0.3404363825381221</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -978,28 +978,28 @@
         <v>0.33</v>
       </c>
       <c r="C16" t="n">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>0.02021289450795234</v>
+        <v>0.01273040509423986</v>
       </c>
       <c r="E16" t="n">
-        <v>0.006972528217519258</v>
+        <v>0.002857709145182241</v>
       </c>
       <c r="F16" t="n">
-        <v>1.52661142936486</v>
+        <v>1.289455804162088</v>
       </c>
       <c r="G16" t="n">
-        <v>0.157</v>
+        <v>0.239</v>
       </c>
       <c r="H16" t="n">
-        <v>39.08929550298586</v>
+        <v>34.74960457066938</v>
       </c>
       <c r="I16" t="n">
-        <v>1933.879162512177</v>
+        <v>2729.654265785507</v>
       </c>
       <c r="J16" t="n">
-        <v>0.521190606706478</v>
+        <v>0.3440554907987067</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1013,28 +1013,28 @@
         <v>0.35</v>
       </c>
       <c r="C17" t="n">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="D17" t="n">
-        <v>0.02435790314121768</v>
+        <v>0.01423172346008342</v>
       </c>
       <c r="E17" t="n">
-        <v>0.01200800318097983</v>
+        <v>0.004932022738008635</v>
       </c>
       <c r="F17" t="n">
-        <v>1.97231582601004</v>
+        <v>1.53034209222471</v>
       </c>
       <c r="G17" t="n">
-        <v>0.056</v>
+        <v>0.176</v>
       </c>
       <c r="H17" t="n">
-        <v>49.38935573607008</v>
+        <v>41.65959791760856</v>
       </c>
       <c r="I17" t="n">
-        <v>2027.652193611648</v>
+        <v>2927.234922351728</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6173669467008761</v>
+        <v>0.3893420366131641</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
@@ -1048,28 +1048,28 @@
         <v>0.37</v>
       </c>
       <c r="C18" t="n">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="D18" t="n">
-        <v>0.02023141148609157</v>
+        <v>0.01406610086915888</v>
       </c>
       <c r="E18" t="n">
-        <v>0.008567499718068805</v>
+        <v>0.005263119626919166</v>
       </c>
       <c r="F18" t="n">
-        <v>1.734530566456884</v>
+        <v>1.597879227739918</v>
       </c>
       <c r="G18" t="n">
-        <v>0.093</v>
+        <v>0.129</v>
       </c>
       <c r="H18" t="n">
-        <v>44.50842495777288</v>
+        <v>43.55232564771364</v>
       </c>
       <c r="I18" t="n">
-        <v>2199.966373496529</v>
+        <v>3096.261433984581</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5236285289149754</v>
+        <v>0.3854188110417133</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
@@ -1083,28 +1083,28 @@
         <v>0.39</v>
       </c>
       <c r="C19" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D19" t="n">
-        <v>0.02489670875664153</v>
+        <v>0.011704197065854</v>
       </c>
       <c r="E19" t="n">
-        <v>0.01381598953796692</v>
+        <v>0.00332880890539522</v>
       </c>
       <c r="F19" t="n">
-        <v>2.246849528926126</v>
+        <v>1.397451299166146</v>
       </c>
       <c r="G19" t="n">
-        <v>0.04</v>
+        <v>0.188</v>
       </c>
       <c r="H19" t="n">
-        <v>55.99365516157191</v>
+        <v>38.46348418958761</v>
       </c>
       <c r="I19" t="n">
-        <v>2249.038445558988</v>
+        <v>3286.298408440298</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6291421928266511</v>
+        <v>0.323222556215022</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
@@ -1118,28 +1118,28 @@
         <v>0.41</v>
       </c>
       <c r="C20" t="n">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="D20" t="n">
-        <v>0.006162699678921424</v>
+        <v>0.01108058253155125</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.00452372290517622</v>
+        <v>0.00316922719180357</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5766850066449825</v>
+        <v>1.400592193840805</v>
       </c>
       <c r="G20" t="n">
-        <v>0.77</v>
+        <v>0.169</v>
       </c>
       <c r="H20" t="n">
-        <v>15.47561277659862</v>
+        <v>38.42085239562122</v>
       </c>
       <c r="I20" t="n">
-        <v>2511.174255258714</v>
+        <v>3467.403657363708</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1646341784744534</v>
+        <v>0.3049273999652476</v>
       </c>
       <c r="K20" t="n">
         <v>1</v>
@@ -1153,28 +1153,28 @@
         <v>0.43</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
-        <v>0.008956144542143706</v>
+        <v>0.01082102286512939</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.001156547860487356</v>
+        <v>0.003270038306848022</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8856340315278882</v>
+        <v>1.433061183162076</v>
       </c>
       <c r="G21" t="n">
-        <v>0.451</v>
+        <v>0.186</v>
       </c>
       <c r="H21" t="n">
-        <v>23.73080638639154</v>
+        <v>38.67900715154192</v>
       </c>
       <c r="I21" t="n">
-        <v>2649.667641553207</v>
+        <v>3574.431699630222</v>
       </c>
       <c r="J21" t="n">
-        <v>0.239705115014056</v>
+        <v>0.2930227814510751</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
@@ -1188,28 +1188,28 @@
         <v>0.45</v>
       </c>
       <c r="C22" t="n">
-        <v>104</v>
+        <v>139</v>
       </c>
       <c r="D22" t="n">
-        <v>0.01105249862390511</v>
+        <v>0.01292195760897726</v>
       </c>
       <c r="E22" t="n">
-        <v>0.001356934884923833</v>
+        <v>0.005717008394444223</v>
       </c>
       <c r="F22" t="n">
-        <v>1.139954201885981</v>
+        <v>1.793483510322675</v>
       </c>
       <c r="G22" t="n">
-        <v>0.301</v>
+        <v>0.095</v>
       </c>
       <c r="H22" t="n">
-        <v>30.43616301258205</v>
+        <v>48.05847497841305</v>
       </c>
       <c r="I22" t="n">
-        <v>2753.781208056667</v>
+        <v>3719.132691243733</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2954967282774958</v>
+        <v>0.3482498186841527</v>
       </c>
       <c r="K22" t="n">
         <v>1</v>
@@ -1223,28 +1223,28 @@
         <v>0.47</v>
       </c>
       <c r="C23" t="n">
-        <v>109</v>
+        <v>145</v>
       </c>
       <c r="D23" t="n">
-        <v>0.01454725286666158</v>
+        <v>0.01427897289482253</v>
       </c>
       <c r="E23" t="n">
-        <v>0.005337414108406158</v>
+        <v>0.007385818859121818</v>
       </c>
       <c r="F23" t="n">
-        <v>1.579533936315848</v>
+        <v>2.071471610944696</v>
       </c>
       <c r="G23" t="n">
-        <v>0.117</v>
+        <v>0.057</v>
       </c>
       <c r="H23" t="n">
-        <v>42.05368176200074</v>
+        <v>54.51901938700233</v>
       </c>
       <c r="I23" t="n">
-        <v>2890.833214178641</v>
+        <v>3818.133124040776</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3893859422407476</v>
+        <v>0.3786043012986272</v>
       </c>
       <c r="K23" t="n">
         <v>1</v>
@@ -1258,28 +1258,28 @@
         <v>0.49</v>
       </c>
       <c r="C24" t="n">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0111382843521153</v>
+        <v>0.01494218291299408</v>
       </c>
       <c r="E24" t="n">
-        <v>0.002309161890973521</v>
+        <v>0.008331056623819499</v>
       </c>
       <c r="F24" t="n">
-        <v>1.26153923010315</v>
+        <v>2.260156932331081</v>
       </c>
       <c r="G24" t="n">
-        <v>0.248</v>
+        <v>0.044</v>
       </c>
       <c r="H24" t="n">
-        <v>33.96646018664569</v>
+        <v>58.80453200825682</v>
       </c>
       <c r="I24" t="n">
-        <v>3049.523527399895</v>
+        <v>3935.471299653211</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3005881432446523</v>
+        <v>0.3920302133883788</v>
       </c>
       <c r="K24" t="n">
         <v>1</v>
@@ -1293,28 +1293,28 @@
         <v>0.51</v>
       </c>
       <c r="C25" t="n">
-        <v>118</v>
+        <v>158</v>
       </c>
       <c r="D25" t="n">
-        <v>0.01184888071673825</v>
+        <v>0.01702255457712617</v>
       </c>
       <c r="E25" t="n">
-        <v>0.003330336584986049</v>
+        <v>0.01072141710646679</v>
       </c>
       <c r="F25" t="n">
-        <v>1.390951380127551</v>
+        <v>2.701505030859876</v>
       </c>
       <c r="G25" t="n">
-        <v>0.197</v>
+        <v>0.017</v>
       </c>
       <c r="H25" t="n">
-        <v>37.81241675340127</v>
+        <v>70.00404212868698</v>
       </c>
       <c r="I25" t="n">
-        <v>3191.22266966413</v>
+        <v>4112.42870813021</v>
       </c>
       <c r="J25" t="n">
-        <v>0.3231830491743698</v>
+        <v>0.445885618654057</v>
       </c>
       <c r="K25" t="n">
         <v>1</v>
@@ -1328,28 +1328,28 @@
         <v>0.53</v>
       </c>
       <c r="C26" t="n">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="D26" t="n">
-        <v>0.01058607599404815</v>
+        <v>0.01598638757806975</v>
       </c>
       <c r="E26" t="n">
-        <v>0.002409101415486559</v>
+        <v>0.009912229476699674</v>
       </c>
       <c r="F26" t="n">
-        <v>1.294620142491669</v>
+        <v>2.63186886335149</v>
       </c>
       <c r="G26" t="n">
-        <v>0.224</v>
+        <v>0.024</v>
       </c>
       <c r="H26" t="n">
-        <v>34.88784623067633</v>
+        <v>68.12446095916563</v>
       </c>
       <c r="I26" t="n">
-        <v>3295.635346873709</v>
+        <v>4261.404312042284</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2859659527104616</v>
+        <v>0.4179414782770898</v>
       </c>
       <c r="K26" t="n">
         <v>1</v>
@@ -1363,28 +1363,28 @@
         <v>0.55</v>
       </c>
       <c r="C27" t="n">
-        <v>128</v>
+        <v>170</v>
       </c>
       <c r="D27" t="n">
-        <v>0.01117586790994968</v>
+        <v>0.01642603037165996</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0033280573378065</v>
+        <v>0.01057142340958661</v>
       </c>
       <c r="F27" t="n">
-        <v>1.424074626574164</v>
+        <v>2.805658941423211</v>
       </c>
       <c r="G27" t="n">
-        <v>0.177</v>
+        <v>0.016</v>
       </c>
       <c r="H27" t="n">
-        <v>38.9520186328758</v>
+        <v>73.27026579698321</v>
       </c>
       <c r="I27" t="n">
-        <v>3485.368559000011</v>
+        <v>4460.619159903498</v>
       </c>
       <c r="J27" t="n">
-        <v>0.3067088081328804</v>
+        <v>0.4335518686212024</v>
       </c>
       <c r="K27" t="n">
         <v>1</v>
@@ -1398,28 +1398,28 @@
         <v>0.57</v>
       </c>
       <c r="C28" t="n">
-        <v>132</v>
+        <v>176</v>
       </c>
       <c r="D28" t="n">
-        <v>0.01279508108919393</v>
+        <v>0.01717480131958564</v>
       </c>
       <c r="E28" t="n">
-        <v>0.005201197097572385</v>
+        <v>0.01152638063751421</v>
       </c>
       <c r="F28" t="n">
-        <v>1.684919219639237</v>
+        <v>3.040637779353117</v>
       </c>
       <c r="G28" t="n">
-        <v>0.112</v>
+        <v>0.011</v>
       </c>
       <c r="H28" t="n">
-        <v>45.39209230439621</v>
+        <v>78.67392258237879</v>
       </c>
       <c r="I28" t="n">
-        <v>3547.620526041999</v>
+        <v>4580.776284885542</v>
       </c>
       <c r="J28" t="n">
-        <v>0.3465045214076047</v>
+        <v>0.4495652718993072</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
@@ -1433,28 +1433,28 @@
         <v>0.59</v>
       </c>
       <c r="C29" t="n">
-        <v>137</v>
+        <v>182</v>
       </c>
       <c r="D29" t="n">
-        <v>0.01201886192957595</v>
+        <v>0.01868681262602617</v>
       </c>
       <c r="E29" t="n">
-        <v>0.004700483129054356</v>
+        <v>0.01323507269617075</v>
       </c>
       <c r="F29" t="n">
-        <v>1.64228475420256</v>
+        <v>3.427678661575805</v>
       </c>
       <c r="G29" t="n">
-        <v>0.118</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>44.20397310442299</v>
+        <v>88.5509503861349</v>
       </c>
       <c r="I29" t="n">
-        <v>3677.883427185905</v>
+        <v>4738.686696242945</v>
       </c>
       <c r="J29" t="n">
-        <v>0.3250292140031103</v>
+        <v>0.4892317700891434</v>
       </c>
       <c r="K29" t="n">
         <v>1</v>
@@ -1468,28 +1468,28 @@
         <v>0.61</v>
       </c>
       <c r="C30" t="n">
-        <v>142</v>
+        <v>189</v>
       </c>
       <c r="D30" t="n">
-        <v>0.008089688255415419</v>
+        <v>0.01836868081915948</v>
       </c>
       <c r="E30" t="n">
-        <v>0.001004614600097042</v>
+        <v>0.01311931547594636</v>
       </c>
       <c r="F30" t="n">
-        <v>1.14179310603819</v>
+        <v>3.499219356661565</v>
       </c>
       <c r="G30" t="n">
-        <v>0.291</v>
+        <v>0.006</v>
       </c>
       <c r="H30" t="n">
-        <v>30.78927007345581</v>
+        <v>90.50969993155597</v>
       </c>
       <c r="I30" t="n">
-        <v>3805.989687284276</v>
+        <v>4927.392490654511</v>
       </c>
       <c r="J30" t="n">
-        <v>0.2183636175422398</v>
+        <v>0.4814345741040215</v>
       </c>
       <c r="K30" t="n">
         <v>1</v>
@@ -1503,28 +1503,28 @@
         <v>0.63</v>
       </c>
       <c r="C31" t="n">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="D31" t="n">
-        <v>0.009698270505655943</v>
+        <v>0.01738860094080295</v>
       </c>
       <c r="E31" t="n">
-        <v>0.002821175161945244</v>
+        <v>0.01229735016847555</v>
       </c>
       <c r="F31" t="n">
-        <v>1.410227722744204</v>
+        <v>3.415388814732027</v>
       </c>
       <c r="G31" t="n">
-        <v>0.157</v>
+        <v>0.004</v>
       </c>
       <c r="H31" t="n">
-        <v>37.63966531187638</v>
+        <v>87.32921871934994</v>
       </c>
       <c r="I31" t="n">
-        <v>3881.069855694917</v>
+        <v>5022.210758453196</v>
       </c>
       <c r="J31" t="n">
-        <v>0.2595838987025956</v>
+        <v>0.4501506119554122</v>
       </c>
       <c r="K31" t="n">
         <v>1</v>
@@ -1538,28 +1538,28 @@
         <v>0.65</v>
       </c>
       <c r="C32" t="n">
-        <v>151</v>
+        <v>201</v>
       </c>
       <c r="D32" t="n">
-        <v>0.009930706036701412</v>
+        <v>0.01580244712214818</v>
       </c>
       <c r="E32" t="n">
-        <v>0.003285945674531554</v>
+        <v>0.01085673077602844</v>
       </c>
       <c r="F32" t="n">
-        <v>1.49451680654118</v>
+        <v>3.195178618471705</v>
       </c>
       <c r="G32" t="n">
-        <v>0.181</v>
+        <v>0.01</v>
       </c>
       <c r="H32" t="n">
-        <v>39.85340503200516</v>
+        <v>82.17488093314311</v>
       </c>
       <c r="I32" t="n">
-        <v>4013.149204569837</v>
+        <v>5200.136428108628</v>
       </c>
       <c r="J32" t="n">
-        <v>0.2656893668800343</v>
+        <v>0.4108744046657154</v>
       </c>
       <c r="K32" t="n">
         <v>1</v>
@@ -1573,28 +1573,28 @@
         <v>0.67</v>
       </c>
       <c r="C33" t="n">
-        <v>156</v>
+        <v>207</v>
       </c>
       <c r="D33" t="n">
-        <v>0.01173671026521023</v>
+        <v>0.01549317277976936</v>
       </c>
       <c r="E33" t="n">
-        <v>0.005319416176023273</v>
+        <v>0.01069070045186582</v>
       </c>
       <c r="F33" t="n">
-        <v>1.828918871738547</v>
+        <v>3.226082676156228</v>
       </c>
       <c r="G33" t="n">
-        <v>0.098</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>49.04564610370941</v>
+        <v>82.71706008368565</v>
       </c>
       <c r="I33" t="n">
-        <v>4178.823963056301</v>
+        <v>5338.936140420233</v>
       </c>
       <c r="J33" t="n">
-        <v>0.3164235232497381</v>
+        <v>0.4015391266198333</v>
       </c>
       <c r="K33" t="n">
         <v>1</v>
@@ -1608,28 +1608,28 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>160</v>
+        <v>213</v>
       </c>
       <c r="D34" t="n">
-        <v>0.01252016915775237</v>
+        <v>0.01534681509394884</v>
       </c>
       <c r="E34" t="n">
-        <v>0.006270296810649501</v>
+        <v>0.01068021232188232</v>
       </c>
       <c r="F34" t="n">
-        <v>2.00326798091423</v>
+        <v>3.288648261603063</v>
       </c>
       <c r="G34" t="n">
-        <v>0.075</v>
+        <v>0.005</v>
       </c>
       <c r="H34" t="n">
-        <v>53.46925951789868</v>
+        <v>84.98712992201445</v>
       </c>
       <c r="I34" t="n">
-        <v>4270.649928462908</v>
+        <v>5537.769850079472</v>
       </c>
       <c r="J34" t="n">
-        <v>0.3362846510559667</v>
+        <v>0.4008826883113887</v>
       </c>
       <c r="K34" t="n">
         <v>1</v>
@@ -1643,28 +1643,28 @@
         <v>0.71</v>
       </c>
       <c r="C35" t="n">
-        <v>165</v>
+        <v>220</v>
       </c>
       <c r="D35" t="n">
-        <v>0.01263425400821769</v>
+        <v>0.01490407707580782</v>
       </c>
       <c r="E35" t="n">
-        <v>0.006576795443851036</v>
+        <v>0.0103852884385407</v>
       </c>
       <c r="F35" t="n">
-        <v>2.085735110519647</v>
+        <v>3.298246116866873</v>
       </c>
       <c r="G35" t="n">
-        <v>0.053</v>
+        <v>0.007</v>
       </c>
       <c r="H35" t="n">
-        <v>56.19034425041148</v>
+        <v>86.54492817227764</v>
       </c>
       <c r="I35" t="n">
-        <v>4447.460389340251</v>
+        <v>5806.795531992831</v>
       </c>
       <c r="J35" t="n">
-        <v>0.3426240503073871</v>
+        <v>0.3951823204213591</v>
       </c>
       <c r="K35" t="n">
         <v>1</v>
@@ -1678,28 +1678,28 @@
         <v>0.73</v>
       </c>
       <c r="C36" t="n">
-        <v>170</v>
+        <v>226</v>
       </c>
       <c r="D36" t="n">
-        <v>0.01269954577927633</v>
+        <v>0.01603627570105617</v>
       </c>
       <c r="E36" t="n">
-        <v>0.006822757361295895</v>
+        <v>0.01164358050329295</v>
       </c>
       <c r="F36" t="n">
-        <v>2.160966990137175</v>
+        <v>3.650668889847445</v>
       </c>
       <c r="G36" t="n">
-        <v>0.055</v>
+        <v>0.002</v>
       </c>
       <c r="H36" t="n">
-        <v>58.09669128316457</v>
+        <v>96.53797548683937</v>
       </c>
       <c r="I36" t="n">
-        <v>4574.706236971821</v>
+        <v>6019.974792556182</v>
       </c>
       <c r="J36" t="n">
-        <v>0.343767404042394</v>
+        <v>0.4290576688303971</v>
       </c>
       <c r="K36" t="n">
         <v>1</v>
@@ -1713,28 +1713,28 @@
         <v>0.75</v>
       </c>
       <c r="C37" t="n">
-        <v>174</v>
+        <v>232</v>
       </c>
       <c r="D37" t="n">
-        <v>0.01041264552989096</v>
+        <v>0.01926863000323399</v>
       </c>
       <c r="E37" t="n">
-        <v>0.004659230678320525</v>
+        <v>0.01500458056846543</v>
       </c>
       <c r="F37" t="n">
-        <v>1.809820045750536</v>
+        <v>4.518857085970882</v>
       </c>
       <c r="G37" t="n">
-        <v>0.082</v>
+        <v>0.004</v>
       </c>
       <c r="H37" t="n">
-        <v>49.20718485225651</v>
+        <v>119.8453769905641</v>
       </c>
       <c r="I37" t="n">
-        <v>4725.714009086392</v>
+        <v>6219.714477388879</v>
       </c>
       <c r="J37" t="n">
-        <v>0.2844345945217138</v>
+        <v>0.5188111558033076</v>
       </c>
       <c r="K37" t="n">
         <v>1</v>
@@ -1748,28 +1748,28 @@
         <v>0.77</v>
       </c>
       <c r="C38" t="n">
-        <v>179</v>
+        <v>238</v>
       </c>
       <c r="D38" t="n">
-        <v>0.00952153771352689</v>
+        <v>0.02069197315552218</v>
       </c>
       <c r="E38" t="n">
-        <v>0.003925614197784033</v>
+        <v>0.01654236287228283</v>
       </c>
       <c r="F38" t="n">
-        <v>1.701513197373111</v>
+        <v>4.986485897024861</v>
       </c>
       <c r="G38" t="n">
-        <v>0.117</v>
+        <v>0.002</v>
       </c>
       <c r="H38" t="n">
-        <v>46.45932948487022</v>
+        <v>133.5927069875524</v>
       </c>
       <c r="I38" t="n">
-        <v>4879.393526832037</v>
+        <v>6456.257505432719</v>
       </c>
       <c r="J38" t="n">
-        <v>0.2610074690161249</v>
+        <v>0.5636823079643561</v>
       </c>
       <c r="K38" t="n">
         <v>1</v>
@@ -1783,28 +1783,28 @@
         <v>0.79</v>
       </c>
       <c r="C39" t="n">
-        <v>184</v>
+        <v>244</v>
       </c>
       <c r="D39" t="n">
-        <v>0.01061112874226849</v>
+        <v>0.01911262849068198</v>
       </c>
       <c r="E39" t="n">
-        <v>0.00517492615294024</v>
+        <v>0.01505937488940368</v>
       </c>
       <c r="F39" t="n">
-        <v>1.951937693252858</v>
+        <v>4.715379389203505</v>
       </c>
       <c r="G39" t="n">
-        <v>0.063</v>
+        <v>0.002</v>
       </c>
       <c r="H39" t="n">
-        <v>53.04389700468506</v>
+        <v>126.2460561554714</v>
       </c>
       <c r="I39" t="n">
-        <v>4998.892982363828</v>
+        <v>6605.373835263965</v>
       </c>
       <c r="J39" t="n">
-        <v>0.289857360681339</v>
+        <v>0.5195310952900057</v>
       </c>
       <c r="K39" t="n">
         <v>1</v>
@@ -1818,28 +1818,28 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="C40" t="n">
-        <v>188</v>
+        <v>251</v>
       </c>
       <c r="D40" t="n">
-        <v>0.00960261598576463</v>
+        <v>0.02066132725813289</v>
       </c>
       <c r="E40" t="n">
-        <v>0.004277898867408481</v>
+        <v>0.01672824021900887</v>
       </c>
       <c r="F40" t="n">
-        <v>1.803403969135029</v>
+        <v>5.253208752465059</v>
       </c>
       <c r="G40" t="n">
-        <v>0.099</v>
+        <v>0.002</v>
       </c>
       <c r="H40" t="n">
-        <v>49.67623754817089</v>
+        <v>139.662203757254</v>
       </c>
       <c r="I40" t="n">
-        <v>5173.198389044535</v>
+        <v>6759.594967563324</v>
       </c>
       <c r="J40" t="n">
-        <v>0.2656483291346036</v>
+        <v>0.558648815029016</v>
       </c>
       <c r="K40" t="n">
         <v>1</v>
@@ -1853,28 +1853,28 @@
         <v>0.83</v>
       </c>
       <c r="C41" t="n">
-        <v>193</v>
+        <v>257</v>
       </c>
       <c r="D41" t="n">
-        <v>0.009220463866310058</v>
+        <v>0.02252194795788607</v>
       </c>
       <c r="E41" t="n">
-        <v>0.004033136451997543</v>
+        <v>0.01868870069497586</v>
       </c>
       <c r="F41" t="n">
-        <v>1.777497954123659</v>
+        <v>5.875422693392108</v>
       </c>
       <c r="G41" t="n">
-        <v>0.128</v>
+        <v>0.001</v>
       </c>
       <c r="H41" t="n">
-        <v>48.68313148299291</v>
+        <v>154.7523257484306</v>
       </c>
       <c r="I41" t="n">
-        <v>5279.900468009256</v>
+        <v>6871.17855159789</v>
       </c>
       <c r="J41" t="n">
-        <v>0.2535579764739214</v>
+        <v>0.6045012724548073</v>
       </c>
       <c r="K41" t="n">
         <v>1</v>
@@ -1888,28 +1888,28 @@
         <v>0.85</v>
       </c>
       <c r="C42" t="n">
-        <v>198</v>
+        <v>263</v>
       </c>
       <c r="D42" t="n">
-        <v>0.009279146731975878</v>
+        <v>0.02321077542258245</v>
       </c>
       <c r="E42" t="n">
-        <v>0.004224448501016553</v>
+        <v>0.01946828797209421</v>
       </c>
       <c r="F42" t="n">
-        <v>1.835746924542879</v>
+        <v>6.201964797384882</v>
       </c>
       <c r="G42" t="n">
-        <v>0.09</v>
+        <v>0.001</v>
       </c>
       <c r="H42" t="n">
-        <v>49.56495394095769</v>
+        <v>162.478532222702</v>
       </c>
       <c r="I42" t="n">
-        <v>5341.542209927255</v>
+        <v>7000.133742391987</v>
       </c>
       <c r="J42" t="n">
-        <v>0.2515987509693285</v>
+        <v>0.6201470695522975</v>
       </c>
       <c r="K42" t="n">
         <v>1</v>
@@ -1923,28 +1923,28 @@
         <v>0.87</v>
       </c>
       <c r="C43" t="n">
-        <v>202</v>
+        <v>269</v>
       </c>
       <c r="D43" t="n">
-        <v>0.009376949373318497</v>
+        <v>0.02639658055456872</v>
       </c>
       <c r="E43" t="n">
-        <v>0.004423834120185099</v>
+        <v>0.0227501258000915</v>
       </c>
       <c r="F43" t="n">
-        <v>1.893141769189908</v>
+        <v>7.238971091622044</v>
       </c>
       <c r="G43" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.001</v>
       </c>
       <c r="H43" t="n">
-        <v>50.84361888870838</v>
+        <v>191.1789056198913</v>
       </c>
       <c r="I43" t="n">
-        <v>5422.191894666788</v>
+        <v>7242.563301889571</v>
       </c>
       <c r="J43" t="n">
-        <v>0.2529533278045193</v>
+        <v>0.7133541254473555</v>
       </c>
       <c r="K43" t="n">
         <v>1</v>
@@ -1958,28 +1958,28 @@
         <v>0.89</v>
       </c>
       <c r="C44" t="n">
-        <v>207</v>
+        <v>275</v>
       </c>
       <c r="D44" t="n">
-        <v>0.009945037353682556</v>
+        <v>0.02521794529687232</v>
       </c>
       <c r="E44" t="n">
-        <v>0.005115500950529817</v>
+        <v>0.02164731505986461</v>
       </c>
       <c r="F44" t="n">
-        <v>2.059211593723642</v>
+        <v>7.062603412557524</v>
       </c>
       <c r="G44" t="n">
-        <v>0.062</v>
+        <v>0.001</v>
       </c>
       <c r="H44" t="n">
-        <v>54.98775644691005</v>
+        <v>185.9529371180976</v>
       </c>
       <c r="I44" t="n">
-        <v>5529.165400927186</v>
+        <v>7373.833788955063</v>
       </c>
       <c r="J44" t="n">
-        <v>0.2669308565383981</v>
+        <v>0.6786603544456113</v>
       </c>
       <c r="K44" t="n">
         <v>1</v>
@@ -1993,28 +1993,28 @@
         <v>0.91</v>
       </c>
       <c r="C45" t="n">
-        <v>212</v>
+        <v>282</v>
       </c>
       <c r="D45" t="n">
-        <v>0.01012880468910244</v>
+        <v>0.02755056403149145</v>
       </c>
       <c r="E45" t="n">
-        <v>0.005415132330479189</v>
+        <v>0.02407753033160398</v>
       </c>
       <c r="F45" t="n">
-        <v>2.148813901028255</v>
+        <v>7.932708522921512</v>
       </c>
       <c r="G45" t="n">
-        <v>0.035</v>
+        <v>0.001</v>
       </c>
       <c r="H45" t="n">
-        <v>57.38866366677688</v>
+        <v>210.3143996119813</v>
       </c>
       <c r="I45" t="n">
-        <v>5665.887084240181</v>
+        <v>7633.760215274838</v>
       </c>
       <c r="J45" t="n">
-        <v>0.2719841879942033</v>
+        <v>0.7484498206832073</v>
       </c>
       <c r="K45" t="n">
         <v>1</v>
@@ -2028,28 +2028,28 @@
         <v>0.93</v>
       </c>
       <c r="C46" t="n">
-        <v>216</v>
+        <v>288</v>
       </c>
       <c r="D46" t="n">
-        <v>0.01067950386429954</v>
+        <v>0.03159451422262909</v>
       </c>
       <c r="E46" t="n">
-        <v>0.006056510891702671</v>
+        <v>0.02820848105557527</v>
       </c>
       <c r="F46" t="n">
-        <v>2.31008438204501</v>
+        <v>9.330834242867184</v>
       </c>
       <c r="G46" t="n">
-        <v>0.041</v>
+        <v>0.001</v>
       </c>
       <c r="H46" t="n">
-        <v>61.55508511026783</v>
+        <v>247.2825640242412</v>
       </c>
       <c r="I46" t="n">
-        <v>5763.852505923987</v>
+        <v>7826.756324904301</v>
       </c>
       <c r="J46" t="n">
-        <v>0.2863027214431061</v>
+        <v>0.8616117213388199</v>
       </c>
       <c r="K46" t="n">
         <v>1</v>
@@ -2063,28 +2063,28 @@
         <v>0.95</v>
       </c>
       <c r="C47" t="n">
-        <v>221</v>
+        <v>294</v>
       </c>
       <c r="D47" t="n">
-        <v>0.01125881751922611</v>
+        <v>0.03166261616163822</v>
       </c>
       <c r="E47" t="n">
-        <v>0.006744017599222607</v>
+        <v>0.02834639224438362</v>
       </c>
       <c r="F47" t="n">
-        <v>2.493757800726039</v>
+        <v>9.547791992239812</v>
       </c>
       <c r="G47" t="n">
-        <v>0.034</v>
+        <v>0.001</v>
       </c>
       <c r="H47" t="n">
-        <v>66.2635817407685</v>
+        <v>254.5326486215339</v>
       </c>
       <c r="I47" t="n">
-        <v>5885.483233706697</v>
+        <v>8038.901375746723</v>
       </c>
       <c r="J47" t="n">
-        <v>0.3011980988216752</v>
+        <v>0.8687121113362928</v>
       </c>
       <c r="K47" t="n">
         <v>1</v>
@@ -2098,28 +2098,28 @@
         <v>0.97</v>
       </c>
       <c r="C48" t="n">
-        <v>226</v>
+        <v>300</v>
       </c>
       <c r="D48" t="n">
-        <v>0.01227300816846976</v>
+        <v>0.03044059879186146</v>
       </c>
       <c r="E48" t="n">
-        <v>0.007863512669221806</v>
+        <v>0.02718704375425018</v>
       </c>
       <c r="F48" t="n">
-        <v>2.783313458549415</v>
+        <v>9.356103843324345</v>
       </c>
       <c r="G48" t="n">
-        <v>0.014</v>
+        <v>0.001</v>
       </c>
       <c r="H48" t="n">
-        <v>73.5738410639634</v>
+        <v>247.8623909357491</v>
       </c>
       <c r="I48" t="n">
-        <v>5994.768361108068</v>
+        <v>8142.493931558833</v>
       </c>
       <c r="J48" t="n">
-        <v>0.3269948491731707</v>
+        <v>0.8289712071429733</v>
       </c>
       <c r="K48" t="n">
         <v>1</v>
@@ -2133,28 +2133,28 @@
         <v>0.99</v>
       </c>
       <c r="C49" t="n">
-        <v>230</v>
+        <v>306</v>
       </c>
       <c r="D49" t="n">
-        <v>0.01379958402038184</v>
+        <v>0.0329821160600596</v>
       </c>
       <c r="E49" t="n">
-        <v>0.009474143599418672</v>
+        <v>0.02980113617867819</v>
       </c>
       <c r="F49" t="n">
-        <v>3.190330388901482</v>
+        <v>10.36853966072136</v>
       </c>
       <c r="G49" t="n">
-        <v>0.007</v>
+        <v>0.001</v>
       </c>
       <c r="H49" t="n">
-        <v>83.58908971965155</v>
+        <v>273.695396620796</v>
       </c>
       <c r="I49" t="n">
-        <v>6057.363004289939</v>
+        <v>8298.297056574651</v>
       </c>
       <c r="J49" t="n">
-        <v>0.3650178590377797</v>
+        <v>0.8973619561337571</v>
       </c>
       <c r="K49" t="n">
         <v>1</v>

--- a/results/01_pollution_assessment/MaxRel_Focus/tables/MaxRel_single_cutoff_metrics.xlsx
+++ b/results/01_pollution_assessment/MaxRel_Focus/tables/MaxRel_single_cutoff_metrics.xlsx
@@ -491,25 +491,25 @@
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07763835896446926</v>
+        <v>0.1055394990897318</v>
       </c>
       <c r="E2" t="n">
-        <v>0.006687463500197666</v>
+        <v>0.03673484517355741</v>
       </c>
       <c r="F2" t="n">
-        <v>1.094254814635359</v>
+        <v>1.533900587863023</v>
       </c>
       <c r="G2" t="n">
-        <v>0.364</v>
+        <v>0.16</v>
       </c>
       <c r="H2" t="n">
-        <v>24.28332371666796</v>
+        <v>34.63526976297067</v>
       </c>
       <c r="I2" t="n">
-        <v>312.7748195680061</v>
+        <v>328.1735280316524</v>
       </c>
       <c r="J2" t="n">
-        <v>1.73452312261914</v>
+        <v>2.473947840212189</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
@@ -526,25 +526,25 @@
         <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01722907575536903</v>
+        <v>0.04086001225511203</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.03449570973119043</v>
+        <v>-0.00962103973146089</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3330912944983782</v>
+        <v>0.8094128518950037</v>
       </c>
       <c r="G3" t="n">
-        <v>0.928</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>7.734815706493755</v>
+        <v>17.41067338648628</v>
       </c>
       <c r="I3" t="n">
-        <v>448.9396771085287</v>
+        <v>426.1054372128343</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3867407853246878</v>
+        <v>0.8705336693243138</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
@@ -561,25 +561,25 @@
         <v>27</v>
       </c>
       <c r="D4" t="n">
-        <v>0.05449831769570292</v>
+        <v>0.03660336970672377</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01667825040353099</v>
+        <v>-0.001932495505007292</v>
       </c>
       <c r="F4" t="n">
-        <v>1.440989442844888</v>
+        <v>0.9498520276010567</v>
       </c>
       <c r="G4" t="n">
-        <v>0.192</v>
+        <v>0.468</v>
       </c>
       <c r="H4" t="n">
-        <v>29.71469348874748</v>
+        <v>24.55714106719447</v>
       </c>
       <c r="I4" t="n">
-        <v>545.2405642071851</v>
+        <v>670.8983698482685</v>
       </c>
       <c r="J4" t="n">
-        <v>1.142872826490288</v>
+        <v>0.9445054256613258</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
@@ -596,25 +596,25 @@
         <v>34</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02525454316955128</v>
+        <v>0.02991893751302763</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.005206252356400265</v>
+        <v>-0.0003960956896902346</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8290835066351208</v>
+        <v>0.9869340176195242</v>
       </c>
       <c r="G5" t="n">
-        <v>0.519</v>
+        <v>0.423</v>
       </c>
       <c r="H5" t="n">
-        <v>19.47134374649659</v>
+        <v>22.66903316561447</v>
       </c>
       <c r="I5" t="n">
-        <v>771.0036018379717</v>
+        <v>757.681757774442</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5900407195908056</v>
+        <v>0.6869403989580142</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
@@ -631,25 +631,25 @@
         <v>40</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008368066182942632</v>
+        <v>0.0306391884172576</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.01772751102276948</v>
+        <v>0.005129693375606426</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3206699019139134</v>
+        <v>1.201089569481124</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.267</v>
       </c>
       <c r="H6" t="n">
-        <v>7.810032493380561</v>
+        <v>28.45949372761289</v>
       </c>
       <c r="I6" t="n">
-        <v>933.3139010420878</v>
+        <v>928.8592550180933</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2002572434200144</v>
+        <v>0.7297306084003305</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
@@ -666,25 +666,25 @@
         <v>46</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02802271415093008</v>
+        <v>0.0217664481531988</v>
       </c>
       <c r="E7" t="n">
-        <v>0.005932321290723963</v>
+        <v>-0.0004661325705921371</v>
       </c>
       <c r="F7" t="n">
-        <v>1.268547568541005</v>
+        <v>0.9790338073486299</v>
       </c>
       <c r="G7" t="n">
-        <v>0.275</v>
+        <v>0.425</v>
       </c>
       <c r="H7" t="n">
-        <v>34.60614743729575</v>
+        <v>21.92007697761888</v>
       </c>
       <c r="I7" t="n">
-        <v>1234.932035880156</v>
+        <v>1007.058056663117</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7690254986065722</v>
+        <v>0.4871128217248643</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
@@ -701,25 +701,25 @@
         <v>52</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01453432716183859</v>
+        <v>0.01179054486316886</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.005174986294924633</v>
+        <v>-0.007973644239567701</v>
       </c>
       <c r="F8" t="n">
-        <v>0.737434471967929</v>
+        <v>0.5965610226597303</v>
       </c>
       <c r="G8" t="n">
-        <v>0.569</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>19.86282721503144</v>
+        <v>13.95956372357876</v>
       </c>
       <c r="I8" t="n">
-        <v>1366.614841805914</v>
+        <v>1183.962563696734</v>
       </c>
       <c r="J8" t="n">
-        <v>0.389467200294734</v>
+        <v>0.2737169357564463</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
@@ -736,25 +736,25 @@
         <v>58</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0167034468117795</v>
+        <v>0.01286812807843111</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0008554202094386287</v>
+        <v>-0.00475922677731111</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9512827218063085</v>
+        <v>0.7300090219854612</v>
       </c>
       <c r="G9" t="n">
-        <v>0.413</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>26.04705252401973</v>
+        <v>16.92868863110987</v>
       </c>
       <c r="I9" t="n">
-        <v>1559.381893900544</v>
+        <v>1315.551766964836</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4569658337547322</v>
+        <v>0.2969945373878923</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
@@ -771,25 +771,25 @@
         <v>65</v>
       </c>
       <c r="D10" t="n">
-        <v>0.009001018187044039</v>
+        <v>0.01064722313760346</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.006729124381415597</v>
+        <v>-0.005056789193545574</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5722146603484644</v>
+        <v>0.6779938090397787</v>
       </c>
       <c r="G10" t="n">
-        <v>0.711</v>
+        <v>0.741</v>
       </c>
       <c r="H10" t="n">
-        <v>15.85535975380239</v>
+        <v>15.47019303525658</v>
       </c>
       <c r="I10" t="n">
-        <v>1761.507356648207</v>
+        <v>1452.979132241488</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2477399961531621</v>
+        <v>0.2417217661758839</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
@@ -806,25 +806,25 @@
         <v>71</v>
       </c>
       <c r="D11" t="n">
-        <v>0.007459376398952546</v>
+        <v>0.01250268482656012</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.006925270319903198</v>
+        <v>-0.001808870465808576</v>
       </c>
       <c r="F11" t="n">
-        <v>0.518565144125132</v>
+        <v>0.8736076947015599</v>
       </c>
       <c r="G11" t="n">
-        <v>0.777</v>
+        <v>0.492</v>
       </c>
       <c r="H11" t="n">
-        <v>14.02531355104338</v>
+        <v>20.09715715088198</v>
       </c>
       <c r="I11" t="n">
-        <v>1880.226013666884</v>
+        <v>1607.4273189858</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2003616221577626</v>
+        <v>0.2871022450125995</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
@@ -841,25 +841,25 @@
         <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>0.01313965245593372</v>
+        <v>0.01092812863239497</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.848551132055398e-05</v>
+        <v>-0.002259496319173104</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9985951271094357</v>
+        <v>0.8286654096191574</v>
       </c>
       <c r="G12" t="n">
-        <v>0.387</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>26.56245483384818</v>
+        <v>19.05858646805894</v>
       </c>
       <c r="I12" t="n">
-        <v>2021.549270266496</v>
+        <v>1743.993606696971</v>
       </c>
       <c r="J12" t="n">
-        <v>0.349505984655897</v>
+        <v>0.2507708745797228</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -876,25 +876,25 @@
         <v>83</v>
       </c>
       <c r="D13" t="n">
-        <v>0.01392162367423972</v>
+        <v>0.01372955402808482</v>
       </c>
       <c r="E13" t="n">
-        <v>0.00174781655910683</v>
+        <v>0.001553375682752489</v>
       </c>
       <c r="F13" t="n">
-        <v>1.143571895182587</v>
+        <v>1.127574977854034</v>
       </c>
       <c r="G13" t="n">
-        <v>0.309</v>
+        <v>0.314</v>
       </c>
       <c r="H13" t="n">
-        <v>31.30188298041526</v>
+        <v>26.61432942155511</v>
       </c>
       <c r="I13" t="n">
-        <v>2248.436225031395</v>
+        <v>1938.470060069943</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3817302802489665</v>
+        <v>0.3245649929457939</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -911,25 +911,25 @@
         <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>0.01320682150051547</v>
+        <v>0.01486375638834495</v>
       </c>
       <c r="E14" t="n">
-        <v>0.001864371172935031</v>
+        <v>0.003540351289360255</v>
       </c>
       <c r="F14" t="n">
-        <v>1.164371111981137</v>
+        <v>1.312657832022445</v>
       </c>
       <c r="G14" t="n">
-        <v>0.283</v>
+        <v>0.205</v>
       </c>
       <c r="H14" t="n">
-        <v>31.88663957785198</v>
+        <v>30.95357871845934</v>
       </c>
       <c r="I14" t="n">
-        <v>2414.406795503932</v>
+        <v>2082.486950790639</v>
       </c>
       <c r="J14" t="n">
-        <v>0.362348177021045</v>
+        <v>0.3517452127097655</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -946,25 +946,25 @@
         <v>96</v>
       </c>
       <c r="D15" t="n">
-        <v>0.01252097777318102</v>
+        <v>0.02069781265523517</v>
       </c>
       <c r="E15" t="n">
-        <v>0.002015881792044594</v>
+        <v>0.01027970427922698</v>
       </c>
       <c r="F15" t="n">
-        <v>1.191895609108617</v>
+        <v>1.986715045401156</v>
       </c>
       <c r="G15" t="n">
-        <v>0.273</v>
+        <v>0.054</v>
       </c>
       <c r="H15" t="n">
-        <v>32.34145634112159</v>
+        <v>48.1087905233328</v>
       </c>
       <c r="I15" t="n">
-        <v>2582.981690966221</v>
+        <v>2324.341771021127</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3404363825381221</v>
+        <v>0.5064083212982399</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -981,25 +981,25 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>0.01273040509423986</v>
+        <v>0.02664289068925876</v>
       </c>
       <c r="E16" t="n">
-        <v>0.002857709145182241</v>
+        <v>0.01690931959615127</v>
       </c>
       <c r="F16" t="n">
-        <v>1.289455804162088</v>
+        <v>2.737216426982823</v>
       </c>
       <c r="G16" t="n">
-        <v>0.239</v>
+        <v>0.01</v>
       </c>
       <c r="H16" t="n">
-        <v>34.74960457066938</v>
+        <v>67.86413247638828</v>
       </c>
       <c r="I16" t="n">
-        <v>2729.654265785507</v>
+        <v>2547.176027853018</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3440554907987067</v>
+        <v>0.671922103726617</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1016,25 +1016,25 @@
         <v>108</v>
       </c>
       <c r="D17" t="n">
-        <v>0.01423172346008342</v>
+        <v>0.02549721533120947</v>
       </c>
       <c r="E17" t="n">
-        <v>0.004932022738008635</v>
+        <v>0.01630379283433403</v>
       </c>
       <c r="F17" t="n">
-        <v>1.53034209222471</v>
+        <v>2.773419294052389</v>
       </c>
       <c r="G17" t="n">
-        <v>0.176</v>
+        <v>0.015</v>
       </c>
       <c r="H17" t="n">
-        <v>41.65959791760856</v>
+        <v>68.9878675927242</v>
       </c>
       <c r="I17" t="n">
-        <v>2927.234922351728</v>
+        <v>2705.70204222579</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3893420366131641</v>
+        <v>0.644746426100226</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
@@ -1051,25 +1051,25 @@
         <v>114</v>
       </c>
       <c r="D18" t="n">
-        <v>0.01406610086915888</v>
+        <v>0.03145626321606802</v>
       </c>
       <c r="E18" t="n">
-        <v>0.005263119626919166</v>
+        <v>0.02280855128049719</v>
       </c>
       <c r="F18" t="n">
-        <v>1.597879227739918</v>
+        <v>3.637524405349152</v>
       </c>
       <c r="G18" t="n">
-        <v>0.129</v>
+        <v>0.003</v>
       </c>
       <c r="H18" t="n">
-        <v>43.55232564771364</v>
+        <v>92.09966905937046</v>
       </c>
       <c r="I18" t="n">
-        <v>3096.261433984581</v>
+        <v>2927.864267499055</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3854188110417133</v>
+        <v>0.8150413191094729</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
@@ -1086,25 +1086,25 @@
         <v>120</v>
       </c>
       <c r="D19" t="n">
-        <v>0.011704197065854</v>
+        <v>0.03093087537476278</v>
       </c>
       <c r="E19" t="n">
-        <v>0.00332880890539522</v>
+        <v>0.02271842516607436</v>
       </c>
       <c r="F19" t="n">
-        <v>1.397451299166146</v>
+        <v>3.766339471019152</v>
       </c>
       <c r="G19" t="n">
-        <v>0.188</v>
+        <v>0.006</v>
       </c>
       <c r="H19" t="n">
-        <v>38.46348418958761</v>
+        <v>96.28572875576563</v>
       </c>
       <c r="I19" t="n">
-        <v>3286.298408440298</v>
+        <v>3112.932550054092</v>
       </c>
       <c r="J19" t="n">
-        <v>0.323222556215022</v>
+        <v>0.8091237710568541</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
@@ -1121,25 +1121,25 @@
         <v>127</v>
       </c>
       <c r="D20" t="n">
-        <v>0.01108058253155125</v>
+        <v>0.0348755699564705</v>
       </c>
       <c r="E20" t="n">
-        <v>0.00316922719180357</v>
+        <v>0.02715457451612224</v>
       </c>
       <c r="F20" t="n">
-        <v>1.400592193840805</v>
+        <v>4.516978442212047</v>
       </c>
       <c r="G20" t="n">
-        <v>0.169</v>
+        <v>0.003</v>
       </c>
       <c r="H20" t="n">
-        <v>38.42085239562122</v>
+        <v>117.8149824997228</v>
       </c>
       <c r="I20" t="n">
-        <v>3467.403657363708</v>
+        <v>3378.152174911323</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3049273999652476</v>
+        <v>0.9350395436485931</v>
       </c>
       <c r="K20" t="n">
         <v>1</v>
@@ -1156,25 +1156,25 @@
         <v>133</v>
       </c>
       <c r="D21" t="n">
-        <v>0.01082102286512939</v>
+        <v>0.03322676755615</v>
       </c>
       <c r="E21" t="n">
-        <v>0.003270038306848022</v>
+        <v>0.02584681921688403</v>
       </c>
       <c r="F21" t="n">
-        <v>1.433061183162076</v>
+        <v>4.502303543151164</v>
       </c>
       <c r="G21" t="n">
-        <v>0.186</v>
+        <v>0.001</v>
       </c>
       <c r="H21" t="n">
-        <v>38.67900715154192</v>
+        <v>117.6052095950239</v>
       </c>
       <c r="I21" t="n">
-        <v>3574.431699630222</v>
+        <v>3539.471885018082</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2930227814510751</v>
+        <v>0.8909485575380593</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
@@ -1191,25 +1191,25 @@
         <v>139</v>
       </c>
       <c r="D22" t="n">
-        <v>0.01292195760897726</v>
+        <v>0.04307333977941569</v>
       </c>
       <c r="E22" t="n">
-        <v>0.005717008394444223</v>
+        <v>0.03608847364641854</v>
       </c>
       <c r="F22" t="n">
-        <v>1.793483510322675</v>
+        <v>6.166666469946274</v>
       </c>
       <c r="G22" t="n">
-        <v>0.095</v>
+        <v>0.001</v>
       </c>
       <c r="H22" t="n">
-        <v>48.05847497841305</v>
+        <v>163.2731841496906</v>
       </c>
       <c r="I22" t="n">
-        <v>3719.132691243733</v>
+        <v>3790.585661242763</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3482498186841527</v>
+        <v>1.183139015577468</v>
       </c>
       <c r="K22" t="n">
         <v>1</v>
@@ -1226,25 +1226,25 @@
         <v>145</v>
       </c>
       <c r="D23" t="n">
-        <v>0.01427897289482253</v>
+        <v>0.03803051728676288</v>
       </c>
       <c r="E23" t="n">
-        <v>0.007385818859121818</v>
+        <v>0.03130345796708978</v>
       </c>
       <c r="F23" t="n">
-        <v>2.071471610944696</v>
+        <v>5.653364342357488</v>
       </c>
       <c r="G23" t="n">
-        <v>0.057</v>
+        <v>0.001</v>
       </c>
       <c r="H23" t="n">
-        <v>54.51901938700233</v>
+        <v>149.139199279561</v>
       </c>
       <c r="I23" t="n">
-        <v>3818.133124040776</v>
+        <v>3921.566413493702</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3786043012986272</v>
+        <v>1.03568888388584</v>
       </c>
       <c r="K23" t="n">
         <v>1</v>
@@ -1261,25 +1261,25 @@
         <v>151</v>
       </c>
       <c r="D24" t="n">
-        <v>0.01494218291299408</v>
+        <v>0.04178133283068997</v>
       </c>
       <c r="E24" t="n">
-        <v>0.008331056623819499</v>
+        <v>0.03535033506445284</v>
       </c>
       <c r="F24" t="n">
-        <v>2.260156932331081</v>
+        <v>6.496866326100096</v>
       </c>
       <c r="G24" t="n">
-        <v>0.044</v>
+        <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>58.80453200825682</v>
+        <v>171.0740904611404</v>
       </c>
       <c r="I24" t="n">
-        <v>3935.471299653211</v>
+        <v>4094.510128587376</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3920302133883788</v>
+        <v>1.140493936407603</v>
       </c>
       <c r="K24" t="n">
         <v>1</v>
@@ -1296,25 +1296,25 @@
         <v>158</v>
       </c>
       <c r="D25" t="n">
-        <v>0.01702255457712617</v>
+        <v>0.03501776453659979</v>
       </c>
       <c r="E25" t="n">
-        <v>0.01072141710646679</v>
+        <v>0.02883198097593698</v>
       </c>
       <c r="F25" t="n">
-        <v>2.701505030859876</v>
+        <v>5.661007080701602</v>
       </c>
       <c r="G25" t="n">
-        <v>0.017</v>
+        <v>0.001</v>
       </c>
       <c r="H25" t="n">
-        <v>70.00404212868698</v>
+        <v>151.0394250657021</v>
       </c>
       <c r="I25" t="n">
-        <v>4112.42870813021</v>
+        <v>4313.222933115535</v>
       </c>
       <c r="J25" t="n">
-        <v>0.445885618654057</v>
+        <v>0.9620345545586121</v>
       </c>
       <c r="K25" t="n">
         <v>1</v>
@@ -1331,25 +1331,25 @@
         <v>164</v>
       </c>
       <c r="D26" t="n">
-        <v>0.01598638757806975</v>
+        <v>0.03971827134568907</v>
       </c>
       <c r="E26" t="n">
-        <v>0.009912229476699674</v>
+        <v>0.03379060635399578</v>
       </c>
       <c r="F26" t="n">
-        <v>2.63186886335149</v>
+        <v>6.700491913991123</v>
       </c>
       <c r="G26" t="n">
-        <v>0.024</v>
+        <v>0.001</v>
       </c>
       <c r="H26" t="n">
-        <v>68.12446095916563</v>
+        <v>180.0591182503902</v>
       </c>
       <c r="I26" t="n">
-        <v>4261.404312042284</v>
+        <v>4533.407727724118</v>
       </c>
       <c r="J26" t="n">
-        <v>0.4179414782770898</v>
+        <v>1.104657167180308</v>
       </c>
       <c r="K26" t="n">
         <v>1</v>
@@ -1366,25 +1366,25 @@
         <v>170</v>
       </c>
       <c r="D27" t="n">
-        <v>0.01642603037165996</v>
+        <v>0.03216747385635864</v>
       </c>
       <c r="E27" t="n">
-        <v>0.01057142340958661</v>
+        <v>0.02640656596264657</v>
       </c>
       <c r="F27" t="n">
-        <v>2.805658941423211</v>
+        <v>5.583750764609241</v>
       </c>
       <c r="G27" t="n">
-        <v>0.016</v>
+        <v>0.001</v>
       </c>
       <c r="H27" t="n">
-        <v>73.27026579698321</v>
+        <v>149.5428987494191</v>
       </c>
       <c r="I27" t="n">
-        <v>4460.619159903498</v>
+        <v>4648.8853746238</v>
       </c>
       <c r="J27" t="n">
-        <v>0.4335518686212024</v>
+        <v>0.8848692233693434</v>
       </c>
       <c r="K27" t="n">
         <v>1</v>
@@ -1401,25 +1401,25 @@
         <v>176</v>
       </c>
       <c r="D28" t="n">
-        <v>0.01717480131958564</v>
+        <v>0.02886884880529913</v>
       </c>
       <c r="E28" t="n">
-        <v>0.01152638063751421</v>
+        <v>0.02328763529268585</v>
       </c>
       <c r="F28" t="n">
-        <v>3.040637779353117</v>
+        <v>5.17250392590378</v>
       </c>
       <c r="G28" t="n">
-        <v>0.011</v>
+        <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>78.67392258237879</v>
+        <v>140.2598927652679</v>
       </c>
       <c r="I28" t="n">
-        <v>4580.776284885542</v>
+        <v>4858.520466514825</v>
       </c>
       <c r="J28" t="n">
-        <v>0.4495652718993072</v>
+        <v>0.8014851015158165</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
@@ -1436,25 +1436,25 @@
         <v>182</v>
       </c>
       <c r="D29" t="n">
-        <v>0.01868681262602617</v>
+        <v>0.02758853368016679</v>
       </c>
       <c r="E29" t="n">
-        <v>0.01323507269617075</v>
+        <v>0.02218624775616773</v>
       </c>
       <c r="F29" t="n">
-        <v>3.427678661575805</v>
+        <v>5.106825900792792</v>
       </c>
       <c r="G29" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.001</v>
       </c>
       <c r="H29" t="n">
-        <v>88.5509503861349</v>
+        <v>138.6816202298426</v>
       </c>
       <c r="I29" t="n">
-        <v>4738.686696242945</v>
+        <v>5026.784744618011</v>
       </c>
       <c r="J29" t="n">
-        <v>0.4892317700891434</v>
+        <v>0.7661967968499588</v>
       </c>
       <c r="K29" t="n">
         <v>1</v>
@@ -1471,25 +1471,25 @@
         <v>189</v>
       </c>
       <c r="D30" t="n">
-        <v>0.01836868081915948</v>
+        <v>0.02386143316285513</v>
       </c>
       <c r="E30" t="n">
-        <v>0.01311931547594636</v>
+        <v>0.01864144082682762</v>
       </c>
       <c r="F30" t="n">
-        <v>3.499219356661565</v>
+        <v>4.571162489677908</v>
       </c>
       <c r="G30" t="n">
-        <v>0.006</v>
+        <v>0.001</v>
       </c>
       <c r="H30" t="n">
-        <v>90.50969993155597</v>
+        <v>123.6019620928921</v>
       </c>
       <c r="I30" t="n">
-        <v>4927.392490654511</v>
+        <v>5179.989032901098</v>
       </c>
       <c r="J30" t="n">
-        <v>0.4814345741040215</v>
+        <v>0.6574572451749577</v>
       </c>
       <c r="K30" t="n">
         <v>1</v>
@@ -1506,25 +1506,25 @@
         <v>195</v>
       </c>
       <c r="D31" t="n">
-        <v>0.01738860094080295</v>
+        <v>0.02309941795163008</v>
       </c>
       <c r="E31" t="n">
-        <v>0.01229735016847555</v>
+        <v>0.01803775690474729</v>
       </c>
       <c r="F31" t="n">
-        <v>3.415388814732027</v>
+        <v>4.563604266993734</v>
       </c>
       <c r="G31" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="H31" t="n">
-        <v>87.32921871934994</v>
+        <v>125.0750248417031</v>
       </c>
       <c r="I31" t="n">
-        <v>5022.210758453196</v>
+        <v>5414.639672030213</v>
       </c>
       <c r="J31" t="n">
-        <v>0.4501506119554122</v>
+        <v>0.6447166228953767</v>
       </c>
       <c r="K31" t="n">
         <v>1</v>
@@ -1541,25 +1541,25 @@
         <v>201</v>
       </c>
       <c r="D32" t="n">
-        <v>0.01580244712214818</v>
+        <v>0.02303288327311607</v>
       </c>
       <c r="E32" t="n">
-        <v>0.01085673077602844</v>
+        <v>0.01812350077700109</v>
       </c>
       <c r="F32" t="n">
-        <v>3.195178618471705</v>
+        <v>4.691604960775207</v>
       </c>
       <c r="G32" t="n">
-        <v>0.01</v>
+        <v>0.001</v>
       </c>
       <c r="H32" t="n">
-        <v>82.17488093314311</v>
+        <v>128.8478926447297</v>
       </c>
       <c r="I32" t="n">
-        <v>5200.136428108628</v>
+        <v>5594.084384351511</v>
       </c>
       <c r="J32" t="n">
-        <v>0.4108744046657154</v>
+        <v>0.6442394632236483</v>
       </c>
       <c r="K32" t="n">
         <v>1</v>
@@ -1576,25 +1576,25 @@
         <v>207</v>
       </c>
       <c r="D33" t="n">
-        <v>0.01549317277976936</v>
+        <v>0.02376057028574486</v>
       </c>
       <c r="E33" t="n">
-        <v>0.01069070045186582</v>
+        <v>0.01899842672616314</v>
       </c>
       <c r="F33" t="n">
-        <v>3.226082676156228</v>
+        <v>4.989469550521445</v>
       </c>
       <c r="G33" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.002</v>
       </c>
       <c r="H33" t="n">
-        <v>82.71706008368565</v>
+        <v>136.529663040119</v>
       </c>
       <c r="I33" t="n">
-        <v>5338.936140420233</v>
+        <v>5746.060022895575</v>
       </c>
       <c r="J33" t="n">
-        <v>0.4015391266198333</v>
+        <v>0.6627653545636846</v>
       </c>
       <c r="K33" t="n">
         <v>1</v>
@@ -1611,25 +1611,25 @@
         <v>213</v>
       </c>
       <c r="D34" t="n">
-        <v>0.01534681509394884</v>
+        <v>0.02047434343927898</v>
       </c>
       <c r="E34" t="n">
-        <v>0.01068021232188232</v>
+        <v>0.01583204174941788</v>
       </c>
       <c r="F34" t="n">
-        <v>3.288648261603063</v>
+        <v>4.410386228020219</v>
       </c>
       <c r="G34" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="H34" t="n">
-        <v>84.98712992201445</v>
+        <v>119.7798537604329</v>
       </c>
       <c r="I34" t="n">
-        <v>5537.769850079472</v>
+        <v>5850.241504235068</v>
       </c>
       <c r="J34" t="n">
-        <v>0.4008826883113887</v>
+        <v>0.5649993101907211</v>
       </c>
       <c r="K34" t="n">
         <v>1</v>
@@ -1646,25 +1646,25 @@
         <v>220</v>
       </c>
       <c r="D35" t="n">
-        <v>0.01490407707580782</v>
+        <v>0.02377002249138967</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0103852884385407</v>
+        <v>0.01929190332850605</v>
       </c>
       <c r="F35" t="n">
-        <v>3.298246116866873</v>
+        <v>5.308037063507656</v>
       </c>
       <c r="G35" t="n">
-        <v>0.007</v>
+        <v>0.002</v>
       </c>
       <c r="H35" t="n">
-        <v>86.54492817227764</v>
+        <v>144.5259016881109</v>
       </c>
       <c r="I35" t="n">
-        <v>5806.795531992831</v>
+        <v>6080.175218196079</v>
       </c>
       <c r="J35" t="n">
-        <v>0.3951823204213591</v>
+        <v>0.659935624146625</v>
       </c>
       <c r="K35" t="n">
         <v>1</v>
@@ -1681,25 +1681,25 @@
         <v>226</v>
       </c>
       <c r="D36" t="n">
-        <v>0.01603627570105617</v>
+        <v>0.02549113487306881</v>
       </c>
       <c r="E36" t="n">
-        <v>0.01164358050329295</v>
+        <v>0.02114064886803779</v>
       </c>
       <c r="F36" t="n">
-        <v>3.650668889847445</v>
+        <v>5.859376364753415</v>
       </c>
       <c r="G36" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H36" t="n">
-        <v>96.53797548683937</v>
+        <v>159.5614225332504</v>
       </c>
       <c r="I36" t="n">
-        <v>6019.974792556182</v>
+        <v>6259.486810915813</v>
       </c>
       <c r="J36" t="n">
-        <v>0.4290576688303971</v>
+        <v>0.7091618779255575</v>
       </c>
       <c r="K36" t="n">
         <v>1</v>
@@ -1716,25 +1716,25 @@
         <v>232</v>
       </c>
       <c r="D37" t="n">
-        <v>0.01926863000323399</v>
+        <v>0.02268621589467024</v>
       </c>
       <c r="E37" t="n">
-        <v>0.01500458056846543</v>
+        <v>0.01843702552899495</v>
       </c>
       <c r="F37" t="n">
-        <v>4.518857085970882</v>
+        <v>5.338950233420432</v>
       </c>
       <c r="G37" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="H37" t="n">
-        <v>119.8453769905641</v>
+        <v>144.1916291131704</v>
       </c>
       <c r="I37" t="n">
-        <v>6219.714477388879</v>
+        <v>6355.913643008478</v>
       </c>
       <c r="J37" t="n">
-        <v>0.5188111558033076</v>
+        <v>0.6242061866371014</v>
       </c>
       <c r="K37" t="n">
         <v>1</v>
@@ -1751,25 +1751,25 @@
         <v>238</v>
       </c>
       <c r="D38" t="n">
-        <v>0.02069197315552218</v>
+        <v>0.02172658921516663</v>
       </c>
       <c r="E38" t="n">
-        <v>0.01654236287228283</v>
+        <v>0.01758136289828183</v>
       </c>
       <c r="F38" t="n">
-        <v>4.986485897024861</v>
+        <v>5.24135175121006</v>
       </c>
       <c r="G38" t="n">
         <v>0.002</v>
       </c>
       <c r="H38" t="n">
-        <v>133.5927069875524</v>
+        <v>141.0984095919925</v>
       </c>
       <c r="I38" t="n">
-        <v>6456.257505432719</v>
+        <v>6494.273362221819</v>
       </c>
       <c r="J38" t="n">
-        <v>0.5636823079643561</v>
+        <v>0.595351939206719</v>
       </c>
       <c r="K38" t="n">
         <v>1</v>
@@ -1786,25 +1786,25 @@
         <v>244</v>
       </c>
       <c r="D39" t="n">
-        <v>0.01911262849068198</v>
+        <v>0.02080179875699373</v>
       </c>
       <c r="E39" t="n">
-        <v>0.01505937488940368</v>
+        <v>0.01675552519813828</v>
       </c>
       <c r="F39" t="n">
-        <v>4.715379389203505</v>
+        <v>5.140976865360062</v>
       </c>
       <c r="G39" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H39" t="n">
-        <v>126.2460561554714</v>
+        <v>138.4786531908637</v>
       </c>
       <c r="I39" t="n">
-        <v>6605.373835263965</v>
+        <v>6657.051864051231</v>
       </c>
       <c r="J39" t="n">
-        <v>0.5195310952900057</v>
+        <v>0.5698710007854473</v>
       </c>
       <c r="K39" t="n">
         <v>1</v>
@@ -1821,25 +1821,25 @@
         <v>251</v>
       </c>
       <c r="D40" t="n">
-        <v>0.02066132725813289</v>
+        <v>0.0232145407903512</v>
       </c>
       <c r="E40" t="n">
-        <v>0.01672824021900887</v>
+        <v>0.01929170762083454</v>
       </c>
       <c r="F40" t="n">
-        <v>5.253208752465059</v>
+        <v>5.917799658355468</v>
       </c>
       <c r="G40" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H40" t="n">
-        <v>139.662203757254</v>
+        <v>158.3028128614458</v>
       </c>
       <c r="I40" t="n">
-        <v>6759.594967563324</v>
+        <v>6819.12316470383</v>
       </c>
       <c r="J40" t="n">
-        <v>0.558648815029016</v>
+        <v>0.6332112514457829</v>
       </c>
       <c r="K40" t="n">
         <v>1</v>
@@ -1856,25 +1856,25 @@
         <v>257</v>
       </c>
       <c r="D41" t="n">
-        <v>0.02252194795788607</v>
+        <v>0.02099813507310136</v>
       </c>
       <c r="E41" t="n">
-        <v>0.01868870069497586</v>
+        <v>0.01715891207338804</v>
       </c>
       <c r="F41" t="n">
-        <v>5.875422693392108</v>
+        <v>5.469371035407234</v>
       </c>
       <c r="G41" t="n">
         <v>0.001</v>
       </c>
       <c r="H41" t="n">
-        <v>154.7523257484306</v>
+        <v>147.1500768568488</v>
       </c>
       <c r="I41" t="n">
-        <v>6871.17855159789</v>
+        <v>7007.768849213101</v>
       </c>
       <c r="J41" t="n">
-        <v>0.6045012724548073</v>
+        <v>0.5748049877220658</v>
       </c>
       <c r="K41" t="n">
         <v>1</v>
@@ -1891,25 +1891,25 @@
         <v>263</v>
       </c>
       <c r="D42" t="n">
-        <v>0.02321077542258245</v>
+        <v>0.02000647937850718</v>
       </c>
       <c r="E42" t="n">
-        <v>0.01946828797209421</v>
+        <v>0.01625171493168154</v>
       </c>
       <c r="F42" t="n">
-        <v>6.201964797384882</v>
+        <v>5.328291471232258</v>
       </c>
       <c r="G42" t="n">
         <v>0.001</v>
       </c>
       <c r="H42" t="n">
-        <v>162.478532222702</v>
+        <v>142.3624073200581</v>
       </c>
       <c r="I42" t="n">
-        <v>7000.133742391987</v>
+        <v>7115.815063043876</v>
       </c>
       <c r="J42" t="n">
-        <v>0.6201470695522975</v>
+        <v>0.5433679668704509</v>
       </c>
       <c r="K42" t="n">
         <v>1</v>
@@ -1926,25 +1926,25 @@
         <v>269</v>
       </c>
       <c r="D43" t="n">
-        <v>0.02639658055456872</v>
+        <v>0.01932079238817381</v>
       </c>
       <c r="E43" t="n">
-        <v>0.0227501258000915</v>
+        <v>0.0156478365544217</v>
       </c>
       <c r="F43" t="n">
-        <v>7.238971091622044</v>
+        <v>5.260284431037221</v>
       </c>
       <c r="G43" t="n">
         <v>0.001</v>
       </c>
       <c r="H43" t="n">
-        <v>191.1789056198913</v>
+        <v>139.8691664794786</v>
       </c>
       <c r="I43" t="n">
-        <v>7242.563301889571</v>
+        <v>7239.307978128889</v>
       </c>
       <c r="J43" t="n">
-        <v>0.7133541254473555</v>
+        <v>0.521899874923428</v>
       </c>
       <c r="K43" t="n">
         <v>1</v>
@@ -1961,25 +1961,25 @@
         <v>275</v>
       </c>
       <c r="D44" t="n">
-        <v>0.02521794529687232</v>
+        <v>0.0200853582967104</v>
       </c>
       <c r="E44" t="n">
-        <v>0.02164731505986461</v>
+        <v>0.01649592737472039</v>
       </c>
       <c r="F44" t="n">
-        <v>7.062603412557524</v>
+        <v>5.595694340754878</v>
       </c>
       <c r="G44" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H44" t="n">
-        <v>185.9529371180976</v>
+        <v>149.4402036466064</v>
       </c>
       <c r="I44" t="n">
-        <v>7373.833788955063</v>
+        <v>7440.255804203493</v>
       </c>
       <c r="J44" t="n">
-        <v>0.6786603544456113</v>
+        <v>0.5454022030898045</v>
       </c>
       <c r="K44" t="n">
         <v>1</v>
@@ -1996,25 +1996,25 @@
         <v>282</v>
       </c>
       <c r="D45" t="n">
-        <v>0.02755056403149145</v>
+        <v>0.01920875581096193</v>
       </c>
       <c r="E45" t="n">
-        <v>0.02407753033160398</v>
+        <v>0.01570592993885822</v>
       </c>
       <c r="F45" t="n">
-        <v>7.932708522921512</v>
+        <v>5.483788378959768</v>
       </c>
       <c r="G45" t="n">
         <v>0.001</v>
       </c>
       <c r="H45" t="n">
-        <v>210.3143996119813</v>
+        <v>146.1304856725342</v>
       </c>
       <c r="I45" t="n">
-        <v>7633.760215274838</v>
+        <v>7607.493536314381</v>
       </c>
       <c r="J45" t="n">
-        <v>0.7484498206832073</v>
+        <v>0.5200373155606194</v>
       </c>
       <c r="K45" t="n">
         <v>1</v>
@@ -2031,25 +2031,25 @@
         <v>288</v>
       </c>
       <c r="D46" t="n">
-        <v>0.03159451422262909</v>
+        <v>0.01834842596512804</v>
       </c>
       <c r="E46" t="n">
-        <v>0.02820848105557527</v>
+        <v>0.01491607780416693</v>
       </c>
       <c r="F46" t="n">
-        <v>9.330834242867184</v>
+        <v>5.345735661032214</v>
       </c>
       <c r="G46" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="H46" t="n">
-        <v>247.2825640242412</v>
+        <v>143.821359623609</v>
       </c>
       <c r="I46" t="n">
-        <v>7826.756324904301</v>
+        <v>7838.348635296975</v>
       </c>
       <c r="J46" t="n">
-        <v>0.8616117213388199</v>
+        <v>0.5011197199428877</v>
       </c>
       <c r="K46" t="n">
         <v>1</v>
@@ -2066,25 +2066,25 @@
         <v>294</v>
       </c>
       <c r="D47" t="n">
-        <v>0.03166261616163822</v>
+        <v>0.01871807973217969</v>
       </c>
       <c r="E47" t="n">
-        <v>0.02834639224438362</v>
+        <v>0.01535752521071465</v>
       </c>
       <c r="F47" t="n">
-        <v>9.547791992239812</v>
+        <v>5.56993782205294</v>
       </c>
       <c r="G47" t="n">
         <v>0.001</v>
       </c>
       <c r="H47" t="n">
-        <v>254.5326486215339</v>
+        <v>149.9257812128967</v>
       </c>
       <c r="I47" t="n">
-        <v>8038.901375746723</v>
+        <v>8009.677453993732</v>
       </c>
       <c r="J47" t="n">
-        <v>0.8687121113362928</v>
+        <v>0.5116920860508416</v>
       </c>
       <c r="K47" t="n">
         <v>1</v>
@@ -2101,25 +2101,25 @@
         <v>300</v>
       </c>
       <c r="D48" t="n">
-        <v>0.03044059879186146</v>
+        <v>0.02119068048675965</v>
       </c>
       <c r="E48" t="n">
-        <v>0.02718704375425018</v>
+        <v>0.01790608545483596</v>
       </c>
       <c r="F48" t="n">
-        <v>9.356103843324345</v>
+        <v>6.451535206259297</v>
       </c>
       <c r="G48" t="n">
         <v>0.001</v>
       </c>
       <c r="H48" t="n">
-        <v>247.8623909357491</v>
+        <v>173.6633978160725</v>
       </c>
       <c r="I48" t="n">
-        <v>8142.493931558833</v>
+        <v>8195.272347416154</v>
       </c>
       <c r="J48" t="n">
-        <v>0.8289712071429733</v>
+        <v>0.580814039518637</v>
       </c>
       <c r="K48" t="n">
         <v>1</v>
@@ -2133,28 +2133,28 @@
         <v>0.99</v>
       </c>
       <c r="C49" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0329821160600596</v>
+        <v>0.02129103354310343</v>
       </c>
       <c r="E49" t="n">
-        <v>0.02980113617867819</v>
+        <v>0.01811340702863296</v>
       </c>
       <c r="F49" t="n">
-        <v>10.36853966072136</v>
+        <v>6.700294526794512</v>
       </c>
       <c r="G49" t="n">
         <v>0.001</v>
       </c>
       <c r="H49" t="n">
-        <v>273.695396620796</v>
+        <v>179.0370196021526</v>
       </c>
       <c r="I49" t="n">
-        <v>8298.297056574651</v>
+        <v>8409.033748394333</v>
       </c>
       <c r="J49" t="n">
-        <v>0.8973619561337571</v>
+        <v>0.5794078304276784</v>
       </c>
       <c r="K49" t="n">
         <v>1</v>
